--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_distance_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_distance_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,8102 +436,5798 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
+          <t>DR-157</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.343419434519526</v>
+        <v>4.092372441727345</v>
       </c>
       <c r="D2" t="n">
-        <v>3.807779349483902</v>
+        <v>3.993222392088213</v>
       </c>
       <c r="E2" t="n">
-        <v>3.017324409786749</v>
+        <v>2.298488697305279</v>
       </c>
       <c r="F2" t="n">
-        <v>3.918030999003999</v>
+        <v>3.20472956295962</v>
       </c>
       <c r="G2" t="n">
-        <v>3.126025008017678</v>
+        <v>4.106007362336312</v>
       </c>
       <c r="H2" t="n">
-        <v>4.014351292894871</v>
+        <v>6.79098583812092</v>
       </c>
       <c r="I2" t="n">
-        <v>5.58981127761724</v>
+        <v>5.498893855158262</v>
       </c>
       <c r="J2" t="n">
-        <v>4.274396122276973</v>
+        <v>4.130811905520041</v>
       </c>
       <c r="K2" t="n">
-        <v>2.311109904070381</v>
+        <v>3.404107866396566</v>
       </c>
       <c r="L2" t="n">
-        <v>1.973417848086996</v>
+        <v>3.147100386635057</v>
       </c>
       <c r="M2" t="n">
-        <v>6.865772530915478</v>
+        <v>3.538280249494909</v>
       </c>
       <c r="N2" t="n">
-        <v>4.517121632713372</v>
+        <v>4.242480962437279</v>
       </c>
       <c r="O2" t="n">
-        <v>3.330413401545536</v>
+        <v>4.104055136462639</v>
       </c>
       <c r="P2" t="n">
-        <v>3.566422276250711</v>
+        <v>3.657819276014251</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.795095871374224</v>
+        <v>5.236510457670192</v>
       </c>
       <c r="R2" t="n">
-        <v>2.777773966889535</v>
+        <v>5.294311113532864</v>
       </c>
       <c r="S2" t="n">
-        <v>2.688105232125184</v>
+        <v>3.847688647130541</v>
       </c>
       <c r="T2" t="n">
-        <v>4.014693514735531</v>
+        <v>3.642660933086359</v>
       </c>
       <c r="U2" t="n">
-        <v>1.201458368442583</v>
+        <v>3.237580104669461</v>
       </c>
       <c r="V2" t="n">
-        <v>1.803455384227065</v>
+        <v>3.17617632885335</v>
       </c>
       <c r="W2" t="n">
-        <v>2.670733770460223</v>
+        <v>3.089182413808422</v>
       </c>
       <c r="X2" t="n">
-        <v>2.740277316576763</v>
+        <v>3.607481714435003</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.72402322859211</v>
+        <v>2.904064855518503</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.792817147489536</v>
+        <v>2.498133994507744</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.319763038761456</v>
+        <v>3.541358357664106</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.561092972636197</v>
+        <v>2.887813106443401</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.953268445221083</v>
+        <v>3.299803636737129</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.034151531117812</v>
+        <v>2.877960413600056</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.83542823355383</v>
+        <v>2.463272442148764</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.137483973817779</v>
+        <v>2.582244207954044</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.109687850100078</v>
+        <v>2.927571835371731</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.52103924422064</v>
+        <v>5.868099003853419</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.167876996721846</v>
+        <v>2.76755078311863</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.793152551379146</v>
+        <v>3.06486120916249</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.66814477546247</v>
+        <v>6.370145365242873</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.127888445093437</v>
+        <v>2.70911501329111</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.159676222668797</v>
+        <v>2.681395002374118</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.613232271592097</v>
+        <v>3.37400989759034</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.879844216681536</v>
+        <v>2.941942855637415</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.624136316022163</v>
+        <v>3.210304018689361</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.200478622861888</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.701429895385591</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.045614037238421</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.596928242262631</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.070553379585092</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.152563112281334</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2.136722083022957</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.614315912258247</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.182601296843855</v>
+        <v>2.424374895912297</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.343419434519526</v>
+        <v>4.092372441727345</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.336391651412837</v>
+        <v>0.9020249095866397</v>
       </c>
       <c r="E3" t="n">
-        <v>1.557749179668444</v>
+        <v>4.304121220299238</v>
       </c>
       <c r="F3" t="n">
-        <v>2.64496493470682</v>
+        <v>3.503252810083388</v>
       </c>
       <c r="G3" t="n">
-        <v>3.587181985952313</v>
+        <v>2.391346726709259</v>
       </c>
       <c r="H3" t="n">
-        <v>2.720588665966813</v>
+        <v>6.463673265379115</v>
       </c>
       <c r="I3" t="n">
-        <v>5.060112345358069</v>
+        <v>4.160605798772013</v>
       </c>
       <c r="J3" t="n">
-        <v>3.11187950660198</v>
+        <v>2.384244314675457</v>
       </c>
       <c r="K3" t="n">
-        <v>3.18434921095909</v>
+        <v>0.8857262599369744</v>
       </c>
       <c r="L3" t="n">
-        <v>3.284650766542616</v>
+        <v>1.934243978972965</v>
       </c>
       <c r="M3" t="n">
-        <v>5.622376005451265</v>
+        <v>0.7268480114121416</v>
       </c>
       <c r="N3" t="n">
-        <v>2.927980700065738</v>
+        <v>2.543332035420879</v>
       </c>
       <c r="O3" t="n">
-        <v>1.634337306732582</v>
+        <v>1.345973886056274</v>
       </c>
       <c r="P3" t="n">
-        <v>2.838650640215675</v>
+        <v>2.30950135878677</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.758111487197069</v>
+        <v>2.775282611530665</v>
       </c>
       <c r="R3" t="n">
-        <v>5.339905307546413</v>
+        <v>3.086775998818675</v>
       </c>
       <c r="S3" t="n">
-        <v>1.248273633469769</v>
+        <v>2.155623856612547</v>
       </c>
       <c r="T3" t="n">
-        <v>3.261512019564386</v>
+        <v>1.902833359204842</v>
       </c>
       <c r="U3" t="n">
-        <v>2.600364923599682</v>
+        <v>2.240045327400948</v>
       </c>
       <c r="V3" t="n">
-        <v>2.982538788559493</v>
+        <v>2.41417477166351</v>
       </c>
       <c r="W3" t="n">
-        <v>2.425075598878268</v>
+        <v>2.288434604335202</v>
       </c>
       <c r="X3" t="n">
-        <v>1.28251346472269</v>
+        <v>2.086902467743083</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.631088009705586</v>
+        <v>2.971860946441493</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.712342499363907</v>
+        <v>2.822129654309585</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.021924490188854</v>
+        <v>1.405997148221669</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.99735272711632</v>
+        <v>2.084402878076655</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.230133515311165</v>
+        <v>1.489735839926417</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.896841526277696</v>
+        <v>2.34632084918824</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.077273393925416</v>
+        <v>1.996660438991536</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.473735044514949</v>
+        <v>1.796871063436556</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.162972798298362</v>
+        <v>2.312801911985534</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.81387117860102</v>
+        <v>3.611878334303272</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.717077660355675</v>
+        <v>1.887586590784991</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.731583596137645</v>
+        <v>1.900078827848789</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.992875543972147</v>
+        <v>3.28176613896112</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.364080612380015</v>
+        <v>1.831465820596917</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.628375060984118</v>
+        <v>2.265862738961046</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.960215476270131</v>
+        <v>2.091640513870106</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.337384359955523</v>
+        <v>2.118072054430893</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.496831622826213</v>
+        <v>4.552272913851311</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.284621996836779</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.717726649208481</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.965485142217091</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.632500214505278</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.829591874728016</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.393834676403988</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.39287407752899</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.69333690752963</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.541830449024862</v>
+        <v>2.304753944810723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.807779349483902</v>
+        <v>3.993222392088213</v>
       </c>
       <c r="C4" t="n">
-        <v>1.336391651412837</v>
+        <v>0.9020249095866397</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2.317773043402036</v>
+        <v>4.360699183222779</v>
       </c>
       <c r="F4" t="n">
-        <v>2.687969565842187</v>
+        <v>3.365834120670357</v>
       </c>
       <c r="G4" t="n">
-        <v>3.147664586908226</v>
+        <v>2.120570372641831</v>
       </c>
       <c r="H4" t="n">
-        <v>2.272673440424494</v>
+        <v>5.981620804191132</v>
       </c>
       <c r="I4" t="n">
-        <v>5.238084354076054</v>
+        <v>4.415018359913537</v>
       </c>
       <c r="J4" t="n">
-        <v>2.144402396316651</v>
+        <v>2.848581037326744</v>
       </c>
       <c r="K4" t="n">
-        <v>2.759677930077371</v>
+        <v>1.251514311599182</v>
       </c>
       <c r="L4" t="n">
-        <v>3.513647650880369</v>
+        <v>1.448320142975178</v>
       </c>
       <c r="M4" t="n">
-        <v>5.539846580404473</v>
+        <v>0.9460355145553655</v>
       </c>
       <c r="N4" t="n">
-        <v>2.953508326277451</v>
+        <v>3.080507916333633</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9789865579232852</v>
+        <v>1.332154731824985</v>
       </c>
       <c r="P4" t="n">
-        <v>3.127387040953227</v>
+        <v>2.642757282665968</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.0040899786247</v>
+        <v>3.087504141028556</v>
       </c>
       <c r="R4" t="n">
-        <v>5.54864324289094</v>
+        <v>3.081815460263112</v>
       </c>
       <c r="S4" t="n">
-        <v>1.77380917302235</v>
+        <v>2.38680284055693</v>
       </c>
       <c r="T4" t="n">
-        <v>3.468513421473021</v>
+        <v>1.60528966651714</v>
       </c>
       <c r="U4" t="n">
-        <v>3.328827573375952</v>
+        <v>2.628905740198753</v>
       </c>
       <c r="V4" t="n">
-        <v>2.846858786269695</v>
+        <v>1.909960645452956</v>
       </c>
       <c r="W4" t="n">
-        <v>2.943050046746678</v>
+        <v>1.707244891185492</v>
       </c>
       <c r="X4" t="n">
-        <v>1.97333565910917</v>
+        <v>2.386810025024726</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.90203541163467</v>
+        <v>3.098437832915537</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.722800896034085</v>
+        <v>3.127964619195395</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.30378626916921</v>
+        <v>1.821525735531988</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.874334651110356</v>
+        <v>2.198125112596649</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.163850902206323</v>
+        <v>1.773812049202641</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.562656112398503</v>
+        <v>2.702520474759384</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.140544253309525</v>
+        <v>2.223894961991335</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.550519824724071</v>
+        <v>2.045880490963417</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.383251952766924</v>
+        <v>2.604477850897752</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.127550928704923</v>
+        <v>4.071936384493574</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.961415797183034</v>
+        <v>1.545111043378842</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.100829954835224</v>
+        <v>2.302649269438164</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.389260439908373</v>
+        <v>3.502768103620437</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.605313598468903</v>
+        <v>2.134625752533136</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.755456461919874</v>
+        <v>2.654490132259402</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.421701285640561</v>
+        <v>2.513421480875125</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.303612949000471</v>
+        <v>2.417203877455667</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.944209178126846</v>
+        <v>3.904776080458087</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.178242272148823</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.119488790312546</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.043256549483683</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.740857884739241</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.107479195044353</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8688440682296441</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.719732166667033</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.841397424373548</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.636378590123875</v>
+        <v>2.559297712195765</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.017324409786749</v>
+        <v>2.298488697305279</v>
       </c>
       <c r="C5" t="n">
-        <v>1.557749179668444</v>
+        <v>4.304121220299238</v>
       </c>
       <c r="D5" t="n">
-        <v>2.317773043402036</v>
+        <v>4.360699183222779</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2.653551557131571</v>
+        <v>1.830888138748817</v>
       </c>
       <c r="G5" t="n">
-        <v>3.773784543015572</v>
+        <v>3.780118530452151</v>
       </c>
       <c r="H5" t="n">
-        <v>2.555336866580916</v>
+        <v>6.706612559520503</v>
       </c>
       <c r="I5" t="n">
-        <v>5.339945085932417</v>
+        <v>5.418095193905038</v>
       </c>
       <c r="J5" t="n">
-        <v>3.368932984300888</v>
+        <v>5.018716594877465</v>
       </c>
       <c r="K5" t="n">
-        <v>3.109128484563614</v>
+        <v>3.53092187057247</v>
       </c>
       <c r="L5" t="n">
-        <v>2.961373957599036</v>
+        <v>3.509456583424858</v>
       </c>
       <c r="M5" t="n">
-        <v>6.424331706492442</v>
+        <v>3.846671492844837</v>
       </c>
       <c r="N5" t="n">
-        <v>3.972696549090261</v>
+        <v>4.721486900193192</v>
       </c>
       <c r="O5" t="n">
-        <v>2.618151970103083</v>
+        <v>3.987178852088539</v>
       </c>
       <c r="P5" t="n">
-        <v>3.525007543847751</v>
+        <v>4.738153606038181</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.541016504518689</v>
+        <v>5.848205022453712</v>
       </c>
       <c r="R5" t="n">
-        <v>5.572072144585829</v>
+        <v>6.051957945879243</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7309367557503257</v>
+        <v>4.635313263265269</v>
       </c>
       <c r="T5" t="n">
-        <v>2.432943259423464</v>
+        <v>4.016650445073632</v>
       </c>
       <c r="U5" t="n">
-        <v>1.976228974368941</v>
+        <v>4.296279356489823</v>
       </c>
       <c r="V5" t="n">
-        <v>2.969539764767302</v>
+        <v>4.250438239422761</v>
       </c>
       <c r="W5" t="n">
-        <v>3.240287238562521</v>
+        <v>3.872741188816127</v>
       </c>
       <c r="X5" t="n">
-        <v>1.926047905706113</v>
+        <v>4.185893245377583</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.45880760671696</v>
+        <v>4.15926879295812</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.348662190685007</v>
+        <v>3.665558987370673</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.205946154392611</v>
+        <v>4.346525737732648</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.617327097903438</v>
+        <v>4.136387204778456</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.569475683494677</v>
+        <v>4.034386795475451</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.018301643032597</v>
+        <v>3.95050666996126</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.44332264317636</v>
+        <v>3.433470227604394</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.451088450655909</v>
+        <v>3.203036052255961</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.746252263254926</v>
+        <v>3.721107695070564</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.839284801822375</v>
+        <v>6.419842103342641</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.307655257729125</v>
+        <v>3.847147639702772</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.163367349694101</v>
+        <v>3.506022759227386</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.166210801047081</v>
+        <v>7.177529601085388</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.768035688314414</v>
+        <v>3.513322839444588</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.426876807829015</v>
+        <v>3.611222067483443</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.067496935318757</v>
+        <v>4.395513974808634</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.967404933060535</v>
+        <v>4.064395053860341</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.108952347642785</v>
+        <v>4.903396226404682</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.813564628997005</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.900793037335625</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.981611117946978</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.370599132386231</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.881993089883172</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.146862541489461</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.615740794276131</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>2.034949927272149</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.290392574695071</v>
+        <v>3.518911049681491</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.918030999003999</v>
+        <v>3.20472956295962</v>
       </c>
       <c r="C6" t="n">
-        <v>2.64496493470682</v>
+        <v>3.503252810083388</v>
       </c>
       <c r="D6" t="n">
-        <v>2.687969565842187</v>
+        <v>3.365834120670357</v>
       </c>
       <c r="E6" t="n">
-        <v>2.653551557131571</v>
+        <v>1.830888138748817</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.533468431536814</v>
+        <v>2.495577208706368</v>
       </c>
       <c r="H6" t="n">
-        <v>1.314944523695304</v>
+        <v>5.667098784274548</v>
       </c>
       <c r="I6" t="n">
-        <v>3.127212085974981</v>
+        <v>4.998621420666248</v>
       </c>
       <c r="J6" t="n">
-        <v>2.370205994238225</v>
+        <v>4.957902143367458</v>
       </c>
       <c r="K6" t="n">
-        <v>3.258178962850493</v>
+        <v>2.876398874910537</v>
       </c>
       <c r="L6" t="n">
-        <v>2.455028926074681</v>
+        <v>2.617054827415971</v>
       </c>
       <c r="M6" t="n">
-        <v>6.537541985416213</v>
+        <v>3.127645923853343</v>
       </c>
       <c r="N6" t="n">
-        <v>4.835695373071924</v>
+        <v>4.628212863459527</v>
       </c>
       <c r="O6" t="n">
-        <v>2.725098469700349</v>
+        <v>2.882087692909177</v>
       </c>
       <c r="P6" t="n">
-        <v>2.312286329691641</v>
+        <v>4.716110902738312</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.236528779716892</v>
+        <v>5.359188447688394</v>
       </c>
       <c r="R6" t="n">
-        <v>5.949342955024231</v>
+        <v>5.429893976803531</v>
       </c>
       <c r="S6" t="n">
-        <v>2.439338284158752</v>
+        <v>4.341234794285475</v>
       </c>
       <c r="T6" t="n">
-        <v>2.279126021744746</v>
+        <v>3.153274497577071</v>
       </c>
       <c r="U6" t="n">
-        <v>3.483067607794611</v>
+        <v>4.382668424198251</v>
       </c>
       <c r="V6" t="n">
-        <v>2.883579824786041</v>
+        <v>3.666013456301735</v>
       </c>
       <c r="W6" t="n">
-        <v>4.415312640899345</v>
+        <v>3.10114269757289</v>
       </c>
       <c r="X6" t="n">
-        <v>3.433097216607355</v>
+        <v>3.926299623559333</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.752968139252077</v>
+        <v>4.375332549111667</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.501925217648454</v>
+        <v>4.079944703497924</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.911004843894611</v>
+        <v>4.074616923241772</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.674429544202387</v>
+        <v>4.082381798732816</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.921385207027513</v>
+        <v>3.715875225306229</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.806042092010863</v>
+        <v>4.13739535484964</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.796646126798873</v>
+        <v>3.479420369584623</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.008577423067319</v>
+        <v>3.090007058603561</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.230239998010522</v>
+        <v>3.753101881182012</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.50165888160974</v>
+        <v>6.116871047886439</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.999851457605303</v>
+        <v>3.40884759825219</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.945072188150091</v>
+        <v>3.386741503848449</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.114607444644896</v>
+        <v>6.546669545961946</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.562460461381697</v>
+        <v>3.476518702638048</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.678952462412513</v>
+        <v>3.838423755427461</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.069209447627083</v>
+        <v>4.433234715499704</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.189237725435067</v>
+        <v>4.13647237391841</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.946622198482324</v>
+        <v>4.650042387887825</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.09401503282264</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.837594288693076</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.398873166510248</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.420767904426287</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.003266562731248</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.024870167969944</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.762279698054969</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.651511387529203</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.64055856367011</v>
+        <v>3.72036675313466</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.126025008017678</v>
+        <v>4.106007362336312</v>
       </c>
       <c r="C7" t="n">
-        <v>3.587181985952313</v>
+        <v>2.391346726709259</v>
       </c>
       <c r="D7" t="n">
-        <v>3.147664586908226</v>
+        <v>2.120570372641831</v>
       </c>
       <c r="E7" t="n">
-        <v>3.773784543015572</v>
+        <v>3.780118530452151</v>
       </c>
       <c r="F7" t="n">
-        <v>2.533468431536814</v>
+        <v>2.495577208706368</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.437238065671113</v>
+        <v>5.55183742847709</v>
       </c>
       <c r="I7" t="n">
-        <v>3.993591952799363</v>
+        <v>4.25844245121765</v>
       </c>
       <c r="J7" t="n">
-        <v>2.15639398355609</v>
+        <v>4.523543146562711</v>
       </c>
       <c r="K7" t="n">
-        <v>1.75819109713335</v>
+        <v>2.432584167365639</v>
       </c>
       <c r="L7" t="n">
-        <v>1.884714945506718</v>
+        <v>2.572532297476862</v>
       </c>
       <c r="M7" t="n">
-        <v>6.542069492878551</v>
+        <v>2.394934361484967</v>
       </c>
       <c r="N7" t="n">
-        <v>4.807710400853995</v>
+        <v>4.337945632948502</v>
       </c>
       <c r="O7" t="n">
-        <v>2.598774308278128</v>
+        <v>1.500701487128307</v>
       </c>
       <c r="P7" t="n">
-        <v>2.730552985109069</v>
+        <v>4.298035341109207</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.413856310156389</v>
+        <v>3.67410693668201</v>
       </c>
       <c r="R7" t="n">
-        <v>4.274478839694962</v>
+        <v>3.293638732456136</v>
       </c>
       <c r="S7" t="n">
-        <v>3.180768930132503</v>
+        <v>2.836294386089678</v>
       </c>
       <c r="T7" t="n">
-        <v>3.605031550094983</v>
+        <v>1.308187751445476</v>
       </c>
       <c r="U7" t="n">
-        <v>3.490534101589233</v>
+        <v>3.839064827839247</v>
       </c>
       <c r="V7" t="n">
-        <v>1.441523728780205</v>
+        <v>2.387334419996338</v>
       </c>
       <c r="W7" t="n">
-        <v>4.059144076668352</v>
+        <v>1.952015516155588</v>
       </c>
       <c r="X7" t="n">
-        <v>3.702436667363802</v>
+        <v>2.564464330067904</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.966567912468372</v>
+        <v>4.585801267519794</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.335623437290228</v>
+        <v>4.020270031740368</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.650538777015433</v>
+        <v>3.182989864591978</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.11643807103719</v>
+        <v>3.547372022106673</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.04463739715662</v>
+        <v>2.849847827008579</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.769248946566149</v>
+        <v>3.76161582746525</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.56749145439984</v>
+        <v>3.101875284964149</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.443874949700824</v>
+        <v>2.868256711916591</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.6813334931568</v>
+        <v>3.482805701109222</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.770187499708779</v>
+        <v>5.102243909230399</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.067895963866187</v>
+        <v>2.837210830600512</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.94501117174642</v>
+        <v>3.049409705696527</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.079734345002512</v>
+        <v>5.240750469309348</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.857955165458317</v>
+        <v>2.915062048010552</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.691155836522928</v>
+        <v>3.531068598370324</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.085038853311533</v>
+        <v>3.856997373728408</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.244162441628913</v>
+        <v>3.604671452484394</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.455439992351216</v>
+        <v>4.499658676005396</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.412448776809675</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.921105747443788</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.598363514542604</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.186842402402223</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.843887757371701</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.028167701801558</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.771190079386263</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.528925360713774</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.575437532632748</v>
+        <v>3.354164965358734</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.014351292894871</v>
+        <v>6.79098583812092</v>
       </c>
       <c r="C8" t="n">
-        <v>2.720588665966813</v>
+        <v>6.463673265379115</v>
       </c>
       <c r="D8" t="n">
-        <v>2.272673440424494</v>
+        <v>5.981620804191132</v>
       </c>
       <c r="E8" t="n">
-        <v>2.555336866580916</v>
+        <v>6.706612559520503</v>
       </c>
       <c r="F8" t="n">
-        <v>1.314944523695304</v>
+        <v>5.667098784274548</v>
       </c>
       <c r="G8" t="n">
-        <v>2.437238065671113</v>
+        <v>5.55183742847709</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.215842265370593</v>
+        <v>5.0203391116547</v>
       </c>
       <c r="J8" t="n">
-        <v>1.464164458728383</v>
+        <v>7.455553430999402</v>
       </c>
       <c r="K8" t="n">
-        <v>2.716487448831392</v>
+        <v>6.245864681532643</v>
       </c>
       <c r="L8" t="n">
-        <v>2.753998256797906</v>
+        <v>5.721100627348627</v>
       </c>
       <c r="M8" t="n">
-        <v>6.633262418274288</v>
+        <v>6.031714885790146</v>
       </c>
       <c r="N8" t="n">
-        <v>4.783944927574899</v>
+        <v>6.681103614706906</v>
       </c>
       <c r="O8" t="n">
-        <v>2.489607557086374</v>
+        <v>5.368614003330993</v>
       </c>
       <c r="P8" t="n">
-        <v>3.147366260998609</v>
+        <v>7.355264518363197</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.603926267320881</v>
+        <v>6.593300463655797</v>
       </c>
       <c r="R8" t="n">
-        <v>6.11714860283061</v>
+        <v>6.959700470600115</v>
       </c>
       <c r="S8" t="n">
-        <v>2.243155359943113</v>
+        <v>6.884266829783558</v>
       </c>
       <c r="T8" t="n">
-        <v>2.233145310441734</v>
+        <v>5.643062360230497</v>
       </c>
       <c r="U8" t="n">
-        <v>3.586936510874631</v>
+        <v>7.09784035478546</v>
       </c>
       <c r="V8" t="n">
-        <v>2.723277672747324</v>
+        <v>5.858416954628398</v>
       </c>
       <c r="W8" t="n">
-        <v>4.533981660583268</v>
+        <v>5.352936798788527</v>
       </c>
       <c r="X8" t="n">
-        <v>3.423984788396662</v>
+        <v>6.730005415120139</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.600601517862083</v>
+        <v>7.301756158817837</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.224465885533756</v>
+        <v>6.981037873740062</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.631110254341277</v>
+        <v>6.801642469285817</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.381203173289457</v>
+        <v>6.813573293419953</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.799044760272983</v>
+        <v>6.225041198818355</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.746567716354166</v>
+        <v>7.015792779171941</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.499200093241177</v>
+        <v>6.730779893603294</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.613664650267925</v>
+        <v>6.215668597559294</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.922560609444316</v>
+        <v>6.155494606809734</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.157943928051839</v>
+        <v>6.8154383556217</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.718705822737599</v>
+        <v>6.008678339481532</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.698884563095074</v>
+        <v>6.142695862557433</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.828985762303552</v>
+        <v>7.40963077222301</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.199416453260925</v>
+        <v>6.67708817367729</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.480309505107764</v>
+        <v>7.086082651461268</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.805560657553781</v>
+        <v>7.390698364220722</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.855351439937112</v>
+        <v>7.268397212953369</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.69099292307357</v>
+        <v>5.928886031383377</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.677928578686425</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.543409903279155</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.158935764112488</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.245460047845185</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.958036585080387</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.600808120316618</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.619029385624564</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.307994920587777</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.543100053573835</v>
+        <v>7.013575698670995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.58981127761724</v>
+        <v>5.498893855158262</v>
       </c>
       <c r="C9" t="n">
-        <v>5.060112345358069</v>
+        <v>4.160605798772013</v>
       </c>
       <c r="D9" t="n">
-        <v>5.238084354076054</v>
+        <v>4.415018359913537</v>
       </c>
       <c r="E9" t="n">
-        <v>5.339945085932417</v>
+        <v>5.418095193905038</v>
       </c>
       <c r="F9" t="n">
-        <v>3.127212085974981</v>
+        <v>4.998621420666248</v>
       </c>
       <c r="G9" t="n">
-        <v>3.993591952799363</v>
+        <v>4.25844245121765</v>
       </c>
       <c r="H9" t="n">
-        <v>4.215842265370593</v>
+        <v>5.0203391116547</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4.625749731894627</v>
+        <v>4.609143294610727</v>
       </c>
       <c r="K9" t="n">
-        <v>5.448640925487169</v>
+        <v>4.097454229655875</v>
       </c>
       <c r="L9" t="n">
-        <v>4.146343966886961</v>
+        <v>4.878430802589885</v>
       </c>
       <c r="M9" t="n">
-        <v>6.725166070319515</v>
+        <v>3.942217553651107</v>
       </c>
       <c r="N9" t="n">
-        <v>6.255256908138428</v>
+        <v>3.404004503272438</v>
       </c>
       <c r="O9" t="n">
-        <v>4.862291949083713</v>
+        <v>3.391336607067394</v>
       </c>
       <c r="P9" t="n">
-        <v>3.489562794029754</v>
+        <v>4.763004593059049</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.282705051199143</v>
+        <v>3.010745150556174</v>
       </c>
       <c r="R9" t="n">
-        <v>6.690448534625398</v>
+        <v>4.337792442735201</v>
       </c>
       <c r="S9" t="n">
-        <v>5.127265697141548</v>
+        <v>3.924018099315758</v>
       </c>
       <c r="T9" t="n">
-        <v>4.266264920602186</v>
+        <v>3.873833390712622</v>
       </c>
       <c r="U9" t="n">
-        <v>5.556835650412341</v>
+        <v>4.142346170889593</v>
       </c>
       <c r="V9" t="n">
-        <v>4.80523964987207</v>
+        <v>4.559550053490721</v>
       </c>
       <c r="W9" t="n">
-        <v>6.083188409934844</v>
+        <v>4.319803761504795</v>
       </c>
       <c r="X9" t="n">
-        <v>5.528732761582249</v>
+        <v>3.681477373434011</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.102422969888434</v>
+        <v>5.34157201749376</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.992049691765914</v>
+        <v>4.189699462825562</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.213738381886453</v>
+        <v>4.027912597433565</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.837747623489021</v>
+        <v>4.498981301902102</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.880199398613457</v>
+        <v>3.512109151691662</v>
       </c>
       <c r="AD9" t="n">
-        <v>6.027295985214432</v>
+        <v>4.136495181224197</v>
       </c>
       <c r="AE9" t="n">
-        <v>5.881970424850311</v>
+        <v>4.236838305804484</v>
       </c>
       <c r="AF9" t="n">
-        <v>6.305724813432653</v>
+        <v>3.760527475866588</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.190591118035172</v>
+        <v>3.315324648404669</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.11120370596357</v>
+        <v>2.856634134179819</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.295374475646561</v>
+        <v>4.511907194140209</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6.26493834688218</v>
+        <v>3.201568873494679</v>
       </c>
       <c r="AK9" t="n">
-        <v>6.565896351557909</v>
+        <v>4.831301709233617</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.165861162284587</v>
+        <v>3.994545548943039</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.763421018149517</v>
+        <v>4.211045446513419</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.518814343796151</v>
+        <v>4.522859221725735</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.76764202136274</v>
+        <v>4.621500958539882</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.522917189828399</v>
+        <v>6.282663321707092</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.829342419473956</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.337934794929509</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.561127963912391</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.763560198457551</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.072674734232137</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.49929650629475</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.170567046187133</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.095394709630816</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.551252427162149</v>
+        <v>4.392194330490327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.274396122276973</v>
+        <v>4.130811905520041</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11187950660198</v>
+        <v>2.384244314675457</v>
       </c>
       <c r="D10" t="n">
-        <v>2.144402396316651</v>
+        <v>2.848581037326744</v>
       </c>
       <c r="E10" t="n">
-        <v>3.368932984300888</v>
+        <v>5.018716594877465</v>
       </c>
       <c r="F10" t="n">
-        <v>2.370205994238225</v>
+        <v>4.957902143367458</v>
       </c>
       <c r="G10" t="n">
-        <v>2.15639398355609</v>
+        <v>4.523543146562711</v>
       </c>
       <c r="H10" t="n">
-        <v>1.464164458728383</v>
+        <v>7.455553430999402</v>
       </c>
       <c r="I10" t="n">
-        <v>4.625749731894627</v>
+        <v>4.609143294610727</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.443699457837595</v>
+        <v>2.310049041762452</v>
       </c>
       <c r="L10" t="n">
-        <v>3.312451291844904</v>
+        <v>3.129729760191235</v>
       </c>
       <c r="M10" t="n">
-        <v>5.944164307158492</v>
+        <v>2.23291568924404</v>
       </c>
       <c r="N10" t="n">
-        <v>4.282731232869631</v>
+        <v>1.435067806587858</v>
       </c>
       <c r="O10" t="n">
-        <v>2.074756284376119</v>
+        <v>3.353282810656604</v>
       </c>
       <c r="P10" t="n">
-        <v>3.616860044520688</v>
+        <v>0.626821190789441</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.926693336203371</v>
+        <v>3.229450383789492</v>
       </c>
       <c r="R10" t="n">
-        <v>5.866658672655327</v>
+        <v>4.127458815170157</v>
       </c>
       <c r="S10" t="n">
-        <v>2.823994049602133</v>
+        <v>2.90277986512254</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04501823590418</v>
+        <v>3.642416052537267</v>
       </c>
       <c r="U10" t="n">
-        <v>4.129663439467472</v>
+        <v>1.316767286023679</v>
       </c>
       <c r="V10" t="n">
-        <v>2.691612763420557</v>
+        <v>3.481664489017313</v>
       </c>
       <c r="W10" t="n">
-        <v>4.44338321270518</v>
+        <v>3.607977559875814</v>
       </c>
       <c r="X10" t="n">
-        <v>3.513191740352305</v>
+        <v>2.985479845391986</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.851602761217847</v>
+        <v>1.722586400366974</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.271011465656105</v>
+        <v>1.953129612859077</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.610349913303997</v>
+        <v>1.503654323823777</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.080244528930492</v>
+        <v>1.628855600792143</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.616445191819501</v>
+        <v>1.901754225476539</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.966295005968251</v>
+        <v>1.579569404448488</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.237325453903068</v>
+        <v>2.071984037014824</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.497344681091107</v>
+        <v>2.11318997126452</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.853871344926323</v>
+        <v>1.92568825500655</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.572829269335234</v>
+        <v>2.941396359700861</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.619218079754964</v>
+        <v>2.454642793750884</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.692581750199519</v>
+        <v>2.058101426917263</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.94019715189531</v>
+        <v>2.769714277409263</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.327908829157866</v>
+        <v>2.123918275193016</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.255378571536125</v>
+        <v>1.872676467275508</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.960209139375868</v>
+        <v>1.196261399387875</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.925998426642234</v>
+        <v>1.660564787349676</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.909138112714628</v>
+        <v>4.829013923097542</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.862461575591942</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.688188974187648</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.930564860698718</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.256042266902419</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.868899520637922</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.39766628262616</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.83027611098738</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.290396672170222</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.449509403476958</v>
+        <v>2.169104641498236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.311109904070381</v>
+        <v>3.404107866396566</v>
       </c>
       <c r="C11" t="n">
-        <v>3.18434921095909</v>
+        <v>0.8857262599369744</v>
       </c>
       <c r="D11" t="n">
-        <v>2.759677930077371</v>
+        <v>1.251514311599182</v>
       </c>
       <c r="E11" t="n">
-        <v>3.109128484563614</v>
+        <v>3.53092187057247</v>
       </c>
       <c r="F11" t="n">
-        <v>3.258178962850493</v>
+        <v>2.876398874910537</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75819109713335</v>
+        <v>2.432584167365639</v>
       </c>
       <c r="H11" t="n">
-        <v>2.716487448831392</v>
+        <v>6.245864681532643</v>
       </c>
       <c r="I11" t="n">
-        <v>5.448640925487169</v>
+        <v>4.097454229655875</v>
       </c>
       <c r="J11" t="n">
-        <v>2.443699457837595</v>
+        <v>2.310049041762452</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.115595178043685</v>
+        <v>1.463171135377593</v>
       </c>
       <c r="M11" t="n">
-        <v>6.645380971742323</v>
+        <v>0.4703526594913956</v>
       </c>
       <c r="N11" t="n">
-        <v>4.360143548580091</v>
+        <v>2.325692309907546</v>
       </c>
       <c r="O11" t="n">
-        <v>2.347427349154816</v>
+        <v>1.450362436878006</v>
       </c>
       <c r="P11" t="n">
-        <v>3.501019479895273</v>
+        <v>2.17142060541289</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.537624484012734</v>
+        <v>3.235775188347287</v>
       </c>
       <c r="R11" t="n">
-        <v>3.874489057659937</v>
+        <v>3.658731705342072</v>
       </c>
       <c r="S11" t="n">
-        <v>2.489734926971351</v>
+        <v>2.43191807533667</v>
       </c>
       <c r="T11" t="n">
-        <v>3.664103233316918</v>
+        <v>2.042204827999064</v>
       </c>
       <c r="U11" t="n">
-        <v>2.626094417885938</v>
+        <v>2.06798192949132</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8943140807148786</v>
+        <v>2.435385985879542</v>
       </c>
       <c r="W11" t="n">
-        <v>3.341116236861381</v>
+        <v>2.187106533903827</v>
       </c>
       <c r="X11" t="n">
-        <v>2.976528239016756</v>
+        <v>2.22910208376958</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.402438486171206</v>
+        <v>2.486562579283467</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.358062068043995</v>
+        <v>2.364480266608161</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.433077020971826</v>
+        <v>1.480944658658535</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.106679267555619</v>
+        <v>1.868860005552528</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.416962878774546</v>
+        <v>1.399670788864011</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.720191884953463</v>
+        <v>2.041990882567362</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.616313965722692</v>
+        <v>1.600898726362088</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.044590980803523</v>
+        <v>1.219411161224731</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.493709688516188</v>
+        <v>1.889050953008158</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.123705458333339</v>
+        <v>3.828698477628884</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.052537643688217</v>
+        <v>1.609804707957751</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.857114784016639</v>
+        <v>1.457892824551916</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.84042316004201</v>
+        <v>3.810849212232521</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.819753231293329</v>
+        <v>1.524473387842974</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.923317345202551</v>
+        <v>1.902574344197026</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.860209570326336</v>
+        <v>1.988928187666916</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.317825261105366</v>
+        <v>1.930018257827868</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.498157234504568</v>
+        <v>4.256243819150352</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.527546603460831</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.747236968117948</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.779732763405617</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.305223563230656</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.085597657593254</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.264966049709135</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.957252498995127</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.374369529490967</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.671619492059961</v>
+        <v>1.954642061405643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.973417848086996</v>
+        <v>3.147100386635057</v>
       </c>
       <c r="C12" t="n">
-        <v>3.284650766542616</v>
+        <v>1.934243978972965</v>
       </c>
       <c r="D12" t="n">
-        <v>3.513647650880369</v>
+        <v>1.448320142975178</v>
       </c>
       <c r="E12" t="n">
-        <v>2.961373957599036</v>
+        <v>3.509456583424858</v>
       </c>
       <c r="F12" t="n">
-        <v>2.455028926074681</v>
+        <v>2.617054827415971</v>
       </c>
       <c r="G12" t="n">
-        <v>1.884714945506718</v>
+        <v>2.572532297476862</v>
       </c>
       <c r="H12" t="n">
-        <v>2.753998256797906</v>
+        <v>5.721100627348627</v>
       </c>
       <c r="I12" t="n">
-        <v>4.146343966886961</v>
+        <v>4.878430802589885</v>
       </c>
       <c r="J12" t="n">
-        <v>3.312451291844904</v>
+        <v>3.129729760191235</v>
       </c>
       <c r="K12" t="n">
-        <v>2.115595178043685</v>
+        <v>1.463171135377593</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.192072453917286</v>
+        <v>1.446933157317519</v>
       </c>
       <c r="N12" t="n">
-        <v>5.138677760457246</v>
+        <v>3.331072632608433</v>
       </c>
       <c r="O12" t="n">
-        <v>3.14410044970366</v>
+        <v>2.075869235610128</v>
       </c>
       <c r="P12" t="n">
-        <v>2.483845947455673</v>
+        <v>2.814080654725952</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.197372543773775</v>
+        <v>4.185972776013521</v>
       </c>
       <c r="R12" t="n">
-        <v>3.967453420566354</v>
+        <v>4.265798956694129</v>
       </c>
       <c r="S12" t="n">
-        <v>2.616432255069839</v>
+        <v>3.256998306978607</v>
       </c>
       <c r="T12" t="n">
-        <v>3.221066958330669</v>
+        <v>2.314454333743118</v>
       </c>
       <c r="U12" t="n">
-        <v>2.167610816842021</v>
+        <v>2.912771168361388</v>
       </c>
       <c r="V12" t="n">
-        <v>1.388915263277528</v>
+        <v>2.22695207720663</v>
       </c>
       <c r="W12" t="n">
-        <v>3.734071361810348</v>
+        <v>1.826299159325883</v>
       </c>
       <c r="X12" t="n">
-        <v>3.360643081064129</v>
+        <v>3.14082756394611</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.841297356117646</v>
+        <v>2.60739051575959</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.151362940337099</v>
+        <v>3.014098238668193</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.293487509045081</v>
+        <v>2.439253529491793</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.204147411820375</v>
+        <v>2.311661838158102</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.119386695982672</v>
+        <v>2.28818481653365</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.069200581254869</v>
+        <v>2.831879165416709</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.565845591870778</v>
+        <v>2.257625015795768</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.163831519452224</v>
+        <v>1.985131336672907</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.255415053506383</v>
+        <v>2.647681899551818</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.534949347828912</v>
+        <v>4.832317244374789</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.917564462519106</v>
+        <v>1.388782601341425</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.641561980152447</v>
+        <v>2.458640476455428</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.602401343169296</v>
+        <v>4.450355848965041</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.592255347602804</v>
+        <v>2.358108193966262</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.731056601669293</v>
+        <v>2.748525036671109</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.552223986129818</v>
+        <v>2.842210017537986</v>
       </c>
       <c r="AO12" t="n">
-        <v>3.111143723723339</v>
+        <v>2.626600139730461</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.106864530829387</v>
+        <v>3.241474707197515</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.271276835817683</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.474169972194221</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.661973002637553</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.005743945846298</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.710688900162207</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.243603066918455</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.371844698353303</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3.293724588143917</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.038170735835759</v>
+        <v>2.608185113972275</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.865772530915478</v>
+        <v>3.538280249494909</v>
       </c>
       <c r="C13" t="n">
-        <v>5.622376005451265</v>
+        <v>0.7268480114121416</v>
       </c>
       <c r="D13" t="n">
-        <v>5.539846580404473</v>
+        <v>0.9460355145553655</v>
       </c>
       <c r="E13" t="n">
-        <v>6.424331706492442</v>
+        <v>3.846671492844837</v>
       </c>
       <c r="F13" t="n">
-        <v>6.537541985416213</v>
+        <v>3.127645923853343</v>
       </c>
       <c r="G13" t="n">
-        <v>6.542069492878551</v>
+        <v>2.394934361484967</v>
       </c>
       <c r="H13" t="n">
-        <v>6.633262418274288</v>
+        <v>6.031714885790146</v>
       </c>
       <c r="I13" t="n">
-        <v>6.725166070319515</v>
+        <v>3.942217553651107</v>
       </c>
       <c r="J13" t="n">
-        <v>5.944164307158492</v>
+        <v>2.23291568924404</v>
       </c>
       <c r="K13" t="n">
-        <v>6.645380971742323</v>
+        <v>0.4703526594913956</v>
       </c>
       <c r="L13" t="n">
-        <v>7.192072453917286</v>
+        <v>1.446933157317519</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.292486827340134</v>
+        <v>2.268272966329728</v>
       </c>
       <c r="O13" t="n">
-        <v>5.019985327248246</v>
+        <v>1.289217267928189</v>
       </c>
       <c r="P13" t="n">
-        <v>6.839303400035825</v>
+        <v>2.084287782378819</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.268140102691233</v>
+        <v>2.932528951171981</v>
       </c>
       <c r="R13" t="n">
-        <v>7.183194830634</v>
+        <v>3.350592057178743</v>
       </c>
       <c r="S13" t="n">
-        <v>6.073293163316658</v>
+        <v>2.240780191618033</v>
       </c>
       <c r="T13" t="n">
-        <v>6.19064998575367</v>
+        <v>1.828446235664499</v>
       </c>
       <c r="U13" t="n">
-        <v>6.810758635976678</v>
+        <v>1.986638321013243</v>
       </c>
       <c r="V13" t="n">
-        <v>6.518351771969902</v>
+        <v>2.167381160815836</v>
       </c>
       <c r="W13" t="n">
-        <v>5.467695147422264</v>
+        <v>1.946376213744655</v>
       </c>
       <c r="X13" t="n">
-        <v>5.097440685247632</v>
+        <v>2.1139740185436</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.295664964291414</v>
+        <v>2.522942024583733</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.373411518212655</v>
+        <v>2.389632169242796</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.778935326976851</v>
+        <v>1.302130325154512</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.401121340102708</v>
+        <v>1.733084442749497</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.603326876996629</v>
+        <v>1.173906885366403</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.100201392499649</v>
+        <v>2.014407112523771</v>
       </c>
       <c r="AE13" t="n">
-        <v>4.794445224069894</v>
+        <v>1.616617486267168</v>
       </c>
       <c r="AF13" t="n">
-        <v>5.936788537430702</v>
+        <v>1.259820818341581</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.672282882642319</v>
+        <v>1.814925619685314</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.78631153900666</v>
+        <v>3.590521055710323</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.256685976832711</v>
+        <v>1.391083684576235</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.574022271722481</v>
+        <v>1.453232121985528</v>
       </c>
       <c r="AK13" t="n">
-        <v>6.213695436131242</v>
+        <v>3.477265489329593</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.931032945631254</v>
+        <v>1.521256280645763</v>
       </c>
       <c r="AM13" t="n">
-        <v>4.692887743974262</v>
+        <v>1.957167825206619</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.229621094489018</v>
+        <v>1.939426568825785</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.069198655213944</v>
+        <v>1.90015002473467</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.222620564969068</v>
+        <v>4.066593577227199</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.24869415485869</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.100967351257824</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.94066498884226</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.117829487833998</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.739145229780394</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.434739148909964</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.872013357577286</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>5.805271511884539</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>7.467247810626188</v>
+        <v>1.982315515276136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.517121632713372</v>
+        <v>4.242480962437279</v>
       </c>
       <c r="C14" t="n">
-        <v>2.927980700065738</v>
+        <v>2.543332035420879</v>
       </c>
       <c r="D14" t="n">
-        <v>2.953508326277451</v>
+        <v>3.080507916333633</v>
       </c>
       <c r="E14" t="n">
-        <v>3.972696549090261</v>
+        <v>4.721486900193192</v>
       </c>
       <c r="F14" t="n">
-        <v>4.835695373071924</v>
+        <v>4.628212863459527</v>
       </c>
       <c r="G14" t="n">
-        <v>4.807710400853995</v>
+        <v>4.337945632948502</v>
       </c>
       <c r="H14" t="n">
-        <v>4.783944927574899</v>
+        <v>6.681103614706906</v>
       </c>
       <c r="I14" t="n">
-        <v>6.255256908138428</v>
+        <v>3.404004503272438</v>
       </c>
       <c r="J14" t="n">
-        <v>4.282731232869631</v>
+        <v>1.435067806587858</v>
       </c>
       <c r="K14" t="n">
-        <v>4.360143548580091</v>
+        <v>2.325692309907546</v>
       </c>
       <c r="L14" t="n">
-        <v>5.138677760457246</v>
+        <v>3.331072632608433</v>
       </c>
       <c r="M14" t="n">
-        <v>3.292486827340134</v>
+        <v>2.268272966329728</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.544496183829526</v>
+        <v>3.006638565660239</v>
       </c>
       <c r="P14" t="n">
-        <v>4.740892337442266</v>
+        <v>1.810600690907362</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.773823137787724</v>
+        <v>2.942702411787991</v>
       </c>
       <c r="R14" t="n">
-        <v>5.297905720095206</v>
+        <v>4.276214140514209</v>
       </c>
       <c r="S14" t="n">
-        <v>3.549792012778568</v>
+        <v>3.074025080917526</v>
       </c>
       <c r="T14" t="n">
-        <v>4.902913330508494</v>
+        <v>3.600016083724037</v>
       </c>
       <c r="U14" t="n">
-        <v>4.300996576945037</v>
+        <v>1.76912768292787</v>
       </c>
       <c r="V14" t="n">
-        <v>4.299046216962889</v>
+        <v>3.76875652204903</v>
       </c>
       <c r="W14" t="n">
-        <v>2.508119689265302</v>
+        <v>3.712180442669688</v>
       </c>
       <c r="X14" t="n">
-        <v>2.252596378381573</v>
+        <v>2.979291097370234</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.707993736174576</v>
+        <v>2.4998073280934</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.321100744364195</v>
+        <v>2.065356390802723</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.847850681126513</v>
+        <v>1.925727477563713</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.50803919211305</v>
+        <v>2.276179443856344</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.207892843921848</v>
+        <v>1.89035914417505</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.174632537173314</v>
+        <v>1.888898035943174</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.113449487623336</v>
+        <v>2.35693546253743</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.17129160141228</v>
+        <v>2.017850603417626</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.510047437280175</v>
+        <v>1.51595842997723</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.430643700031561</v>
+        <v>2.159958581877348</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.188358789437952</v>
+        <v>2.84575137576105</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.524177029654865</v>
+        <v>1.569013170743587</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.137789735622434</v>
+        <v>3.071349467835561</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.929937141320415</v>
+        <v>2.29006114173616</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.748602521614415</v>
+        <v>2.126276552599873</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.178896565444341</v>
+        <v>1.98326821043841</v>
       </c>
       <c r="AO14" t="n">
-        <v>3.104831284800083</v>
+        <v>2.346713849899271</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.108771544587116</v>
+        <v>5.2498844488108</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.329634530563882</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>3.065947649089136</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.739835409601472</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.100668506207317</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.576035594089041</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.661645395642367</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>3.176537389324415</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.824109287017292</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>5.467600645643432</v>
+        <v>2.514726048841695</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.330413401545536</v>
+        <v>4.104055136462639</v>
       </c>
       <c r="C15" t="n">
-        <v>1.634337306732582</v>
+        <v>1.345973886056274</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9789865579232852</v>
+        <v>1.332154731824985</v>
       </c>
       <c r="E15" t="n">
-        <v>2.618151970103083</v>
+        <v>3.987178852088539</v>
       </c>
       <c r="F15" t="n">
-        <v>2.725098469700349</v>
+        <v>2.882087692909177</v>
       </c>
       <c r="G15" t="n">
-        <v>2.598774308278128</v>
+        <v>1.500701487128307</v>
       </c>
       <c r="H15" t="n">
-        <v>2.489607557086374</v>
+        <v>5.368614003330993</v>
       </c>
       <c r="I15" t="n">
-        <v>4.862291949083713</v>
+        <v>3.391336607067394</v>
       </c>
       <c r="J15" t="n">
-        <v>2.074756284376119</v>
+        <v>3.353282810656604</v>
       </c>
       <c r="K15" t="n">
-        <v>2.347427349154816</v>
+        <v>1.450362436878006</v>
       </c>
       <c r="L15" t="n">
-        <v>3.14410044970366</v>
+        <v>2.075869235610128</v>
       </c>
       <c r="M15" t="n">
-        <v>5.019985327248246</v>
+        <v>1.289217267928189</v>
       </c>
       <c r="N15" t="n">
-        <v>2.544496183829526</v>
+        <v>3.006638565660239</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.888627387005863</v>
+        <v>3.269097767857315</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.769751028401272</v>
+        <v>2.802998579100026</v>
       </c>
       <c r="R15" t="n">
-        <v>4.776880357818158</v>
+        <v>3.104161560061837</v>
       </c>
       <c r="S15" t="n">
-        <v>1.945254019625723</v>
+        <v>2.422785890282305</v>
       </c>
       <c r="T15" t="n">
-        <v>3.475126179548313</v>
+        <v>1.375980026380142</v>
       </c>
       <c r="U15" t="n">
-        <v>3.112820443753023</v>
+        <v>2.9343221846754</v>
       </c>
       <c r="V15" t="n">
-        <v>2.311425886491544</v>
+        <v>2.357278841502209</v>
       </c>
       <c r="W15" t="n">
-        <v>2.490489250186267</v>
+        <v>1.952953062752409</v>
       </c>
       <c r="X15" t="n">
-        <v>1.755762064262472</v>
+        <v>2.192134524547235</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.621503895821529</v>
+        <v>3.743225696081289</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.799840653809223</v>
+        <v>3.262132182385281</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.101473039413135</v>
+        <v>2.226364082098928</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.415870512949522</v>
+        <v>2.777954848334646</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.472695237202685</v>
+        <v>1.870390769565178</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.399541302860467</v>
+        <v>2.937370362681257</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.74197342923425</v>
+        <v>2.484558682822073</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.264162064925697</v>
+        <v>2.05702834449341</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.959310141703846</v>
+        <v>2.502132118092772</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.76547992646932</v>
+        <v>3.791601909831546</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.923098178894712</v>
+        <v>2.243086575922804</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.029062931972775</v>
+        <v>2.040923941394796</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.429388262706389</v>
+        <v>3.977273501799498</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.899102313065016</v>
+        <v>2.269259148966144</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.450164436554436</v>
+        <v>2.826998306972636</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.46497217248785</v>
+        <v>2.987009438228443</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.481101189934132</v>
+        <v>2.909599783234684</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.390136753845732</v>
+        <v>4.523007796616731</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.652661530386227</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.20973146361895</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.123802672383694</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.629600296830036</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.933334282507433</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.8718411042912625</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.508983205136552</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.785268075104492</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.461268247312252</v>
+        <v>2.812233016006298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.566422276250711</v>
+        <v>3.657819276014251</v>
       </c>
       <c r="C16" t="n">
-        <v>2.838650640215675</v>
+        <v>2.30950135878677</v>
       </c>
       <c r="D16" t="n">
-        <v>3.127387040953227</v>
+        <v>2.642757282665968</v>
       </c>
       <c r="E16" t="n">
-        <v>3.525007543847751</v>
+        <v>4.738153606038181</v>
       </c>
       <c r="F16" t="n">
-        <v>2.312286329691641</v>
+        <v>4.716110902738312</v>
       </c>
       <c r="G16" t="n">
-        <v>2.730552985109069</v>
+        <v>4.298035341109207</v>
       </c>
       <c r="H16" t="n">
-        <v>3.147366260998609</v>
+        <v>7.355264518363197</v>
       </c>
       <c r="I16" t="n">
-        <v>3.489562794029754</v>
+        <v>4.763004593059049</v>
       </c>
       <c r="J16" t="n">
-        <v>3.616860044520688</v>
+        <v>0.626821190789441</v>
       </c>
       <c r="K16" t="n">
-        <v>3.501019479895273</v>
+        <v>2.17142060541289</v>
       </c>
       <c r="L16" t="n">
-        <v>2.483845947455673</v>
+        <v>2.814080654725952</v>
       </c>
       <c r="M16" t="n">
-        <v>6.839303400035825</v>
+        <v>2.084287782378819</v>
       </c>
       <c r="N16" t="n">
-        <v>4.740892337442266</v>
+        <v>1.810600690907362</v>
       </c>
       <c r="O16" t="n">
-        <v>2.888627387005863</v>
+        <v>3.269097767857315</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.351441076233492</v>
+        <v>3.295825929865082</v>
       </c>
       <c r="R16" t="n">
-        <v>4.863360487559467</v>
+        <v>3.960720109505604</v>
       </c>
       <c r="S16" t="n">
-        <v>3.167951486727213</v>
+        <v>2.664907120557442</v>
       </c>
       <c r="T16" t="n">
-        <v>4.233203844516392</v>
+        <v>3.36200238561123</v>
       </c>
       <c r="U16" t="n">
-        <v>3.459181748944077</v>
+        <v>1.031645237471527</v>
       </c>
       <c r="V16" t="n">
-        <v>2.846609418540874</v>
+        <v>3.03776669666784</v>
       </c>
       <c r="W16" t="n">
-        <v>3.570893730134001</v>
+        <v>3.211177472408056</v>
       </c>
       <c r="X16" t="n">
-        <v>3.452259482510446</v>
+        <v>2.769032761183354</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.977622992833588</v>
+        <v>1.305597074361694</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.152651743429274</v>
+        <v>1.642340695738873</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.889581182457428</v>
+        <v>1.284301449746412</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.515934524714113</v>
+        <v>1.0979120544735</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.842981414988542</v>
+        <v>1.698449660304101</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.562139313472837</v>
+        <v>1.254868508149009</v>
       </c>
       <c r="AE16" t="n">
-        <v>4.065876223213546</v>
+        <v>1.664021977794225</v>
       </c>
       <c r="AF16" t="n">
-        <v>4.097791976501092</v>
+        <v>1.844794021013509</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.658406425696818</v>
+        <v>1.778351826222712</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.496012967409215</v>
+        <v>3.324560657640434</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.070892406072132</v>
+        <v>1.995556006617987</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.924880854956946</v>
+        <v>1.967539680142923</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.022197561836952</v>
+        <v>3.071042251314517</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.765657757995385</v>
+        <v>1.791325262639618</v>
       </c>
       <c r="AM16" t="n">
-        <v>3.778766747190505</v>
+        <v>1.551012934133084</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.001754728045382</v>
+        <v>0.8459195868872418</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.173238181782653</v>
+        <v>1.194326696529445</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.931559812004689</v>
+        <v>4.287265726399268</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.290156757359957</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>3.860120429726317</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.330048376102801</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.967574562539701</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.293671085975035</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.301243229397302</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.879242668282736</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.70142683645913</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.089477167424934</v>
+        <v>1.745986676732899</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.795095871374224</v>
+        <v>5.236510457670192</v>
       </c>
       <c r="C17" t="n">
-        <v>1.758111487197069</v>
+        <v>2.775282611530665</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0040899786247</v>
+        <v>3.087504141028556</v>
       </c>
       <c r="E17" t="n">
-        <v>2.541016504518689</v>
+        <v>5.848205022453712</v>
       </c>
       <c r="F17" t="n">
-        <v>2.236528779716892</v>
+        <v>5.359188447688394</v>
       </c>
       <c r="G17" t="n">
-        <v>2.413856310156389</v>
+        <v>3.67410693668201</v>
       </c>
       <c r="H17" t="n">
-        <v>2.603926267320881</v>
+        <v>6.593300463655797</v>
       </c>
       <c r="I17" t="n">
-        <v>4.282705051199143</v>
+        <v>3.010745150556174</v>
       </c>
       <c r="J17" t="n">
-        <v>2.926693336203371</v>
+        <v>3.229450383789492</v>
       </c>
       <c r="K17" t="n">
-        <v>2.537624484012734</v>
+        <v>3.235775188347287</v>
       </c>
       <c r="L17" t="n">
-        <v>2.197372543773775</v>
+        <v>4.185972776013521</v>
       </c>
       <c r="M17" t="n">
-        <v>6.268140102691233</v>
+        <v>2.932528951171981</v>
       </c>
       <c r="N17" t="n">
-        <v>3.773823137787724</v>
+        <v>2.942702411787991</v>
       </c>
       <c r="O17" t="n">
-        <v>1.769751028401272</v>
+        <v>2.802998579100026</v>
       </c>
       <c r="P17" t="n">
-        <v>1.351441076233492</v>
+        <v>3.295825929865082</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.422556191885581</v>
+        <v>1.796374372641999</v>
       </c>
       <c r="S17" t="n">
-        <v>2.040822381314439</v>
+        <v>1.828080591028004</v>
       </c>
       <c r="T17" t="n">
-        <v>3.70240440238952</v>
+        <v>2.714056297736276</v>
       </c>
       <c r="U17" t="n">
-        <v>2.562122834496294</v>
+        <v>2.724063217597378</v>
       </c>
       <c r="V17" t="n">
-        <v>2.037970795194373</v>
+        <v>3.150853914414793</v>
       </c>
       <c r="W17" t="n">
-        <v>2.55198958886447</v>
+        <v>3.329691554986308</v>
       </c>
       <c r="X17" t="n">
-        <v>2.265484463217816</v>
+        <v>2.018265707127957</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.102079342174751</v>
+        <v>4.368700818642172</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.847887952560944</v>
+        <v>3.379813664111801</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.589165118568488</v>
+        <v>2.354305965065915</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.222383074563708</v>
+        <v>3.048906792428466</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.741271340028113</v>
+        <v>2.220558317391023</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.358564425438321</v>
+        <v>2.940808920954778</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.824610178454943</v>
+        <v>3.088354697371261</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.814121251857993</v>
+        <v>3.047853194792874</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.537244902037281</v>
+        <v>2.784276625587514</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.463552346461784</v>
+        <v>2.162834565408593</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.779173366544244</v>
+        <v>3.340237159847848</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.62513371542644</v>
+        <v>2.686478236163066</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.725772797452833</v>
+        <v>2.934726800205464</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.455112299694319</v>
+        <v>2.794524287438581</v>
       </c>
       <c r="AM17" t="n">
-        <v>2.550174986022399</v>
+        <v>3.075579354777991</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.716432893098393</v>
+        <v>2.908138184188437</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.835723252002751</v>
+        <v>3.066696348754805</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.709759584025474</v>
+        <v>5.46042507619392</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.002849794740383</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.553178532138805</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>3.132438770400412</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.6554130928955</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.116254572979454</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.006903166698121</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.599574616886748</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2.363081595721432</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.199596059997461</v>
+        <v>3.169791953336476</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.777773966889535</v>
+        <v>5.294311113532864</v>
       </c>
       <c r="C18" t="n">
-        <v>5.339905307546413</v>
+        <v>3.086775998818675</v>
       </c>
       <c r="D18" t="n">
-        <v>5.54864324289094</v>
+        <v>3.081815460263112</v>
       </c>
       <c r="E18" t="n">
-        <v>5.572072144585829</v>
+        <v>6.051957945879243</v>
       </c>
       <c r="F18" t="n">
-        <v>5.949342955024231</v>
+        <v>5.429893976803531</v>
       </c>
       <c r="G18" t="n">
-        <v>4.274478839694962</v>
+        <v>3.293638732456136</v>
       </c>
       <c r="H18" t="n">
-        <v>6.11714860283061</v>
+        <v>6.959700470600115</v>
       </c>
       <c r="I18" t="n">
-        <v>6.690448534625398</v>
+        <v>4.337792442735201</v>
       </c>
       <c r="J18" t="n">
-        <v>5.866658672655327</v>
+        <v>4.127458815170157</v>
       </c>
       <c r="K18" t="n">
-        <v>3.874489057659937</v>
+        <v>3.658731705342072</v>
       </c>
       <c r="L18" t="n">
-        <v>3.967453420566354</v>
+        <v>4.265798956694129</v>
       </c>
       <c r="M18" t="n">
-        <v>7.183194830634</v>
+        <v>3.350592057178743</v>
       </c>
       <c r="N18" t="n">
-        <v>5.297905720095206</v>
+        <v>4.276214140514209</v>
       </c>
       <c r="O18" t="n">
-        <v>4.776880357818158</v>
+        <v>3.104161560061837</v>
       </c>
       <c r="P18" t="n">
-        <v>4.863360487559467</v>
+        <v>3.960720109505604</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.422556191885581</v>
+        <v>1.796374372641999</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5.091657489665412</v>
+        <v>1.703391216244606</v>
       </c>
       <c r="T18" t="n">
-        <v>6.352034734958242</v>
+        <v>2.333175474378257</v>
       </c>
       <c r="U18" t="n">
-        <v>3.88096710127998</v>
+        <v>3.401985219377492</v>
       </c>
       <c r="V18" t="n">
-        <v>3.460590487408037</v>
+        <v>2.610265350633689</v>
       </c>
       <c r="W18" t="n">
-        <v>3.558271115439733</v>
+        <v>2.972542298694829</v>
       </c>
       <c r="X18" t="n">
-        <v>4.533758219583625</v>
+        <v>2.074986517129707</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.529733061097079</v>
+        <v>4.887703937921181</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.48914804852778</v>
+        <v>4.038217935741987</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.123134129991026</v>
+        <v>2.880674854414857</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.964284135006604</v>
+        <v>3.383797829415955</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.548134739014785</v>
+        <v>2.828332132066314</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.025523607428865</v>
+        <v>3.567090430787848</v>
       </c>
       <c r="AE18" t="n">
-        <v>4.402418372502093</v>
+        <v>3.408285552856515</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.91463956926683</v>
+        <v>3.58769774518928</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.922730774371407</v>
+        <v>3.665888003967494</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.73687900375859</v>
+        <v>3.91129883944127</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.81198395253496</v>
+        <v>3.399706066324322</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.535716983273317</v>
+        <v>3.536934684978274</v>
       </c>
       <c r="AK18" t="n">
-        <v>4.53339483865706</v>
+        <v>3.85644526774809</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.099806812551913</v>
+        <v>3.151722375618288</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.66373111216954</v>
+        <v>3.587473988483855</v>
       </c>
       <c r="AN18" t="n">
-        <v>4.543667335878508</v>
+        <v>3.44393431773595</v>
       </c>
       <c r="AO18" t="n">
-        <v>4.742537203138858</v>
+        <v>3.382737999607018</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.510025446546909</v>
+        <v>5.050293010135589</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.184483652090709</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.666914486592042</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.395491410928596</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.218418245858501</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4.293296398739748</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.879217914717471</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.250500399237159</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.456058947663544</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>5.054458878015742</v>
+        <v>3.454594480009683</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.688105232125184</v>
+        <v>3.847688647130541</v>
       </c>
       <c r="C19" t="n">
-        <v>1.248273633469769</v>
+        <v>2.155623856612547</v>
       </c>
       <c r="D19" t="n">
-        <v>1.77380917302235</v>
+        <v>2.38680284055693</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7309367557503257</v>
+        <v>4.635313263265269</v>
       </c>
       <c r="F19" t="n">
-        <v>2.439338284158752</v>
+        <v>4.341234794285475</v>
       </c>
       <c r="G19" t="n">
-        <v>3.180768930132503</v>
+        <v>2.836294386089678</v>
       </c>
       <c r="H19" t="n">
-        <v>2.243155359943113</v>
+        <v>6.884266829783558</v>
       </c>
       <c r="I19" t="n">
-        <v>5.127265697141548</v>
+        <v>3.924018099315758</v>
       </c>
       <c r="J19" t="n">
-        <v>2.823994049602133</v>
+        <v>2.90277986512254</v>
       </c>
       <c r="K19" t="n">
-        <v>2.489734926971351</v>
+        <v>2.43191807533667</v>
       </c>
       <c r="L19" t="n">
-        <v>2.616432255069839</v>
+        <v>3.256998306978607</v>
       </c>
       <c r="M19" t="n">
-        <v>6.073293163316658</v>
+        <v>2.240780191618033</v>
       </c>
       <c r="N19" t="n">
-        <v>3.549792012778568</v>
+        <v>3.074025080917526</v>
       </c>
       <c r="O19" t="n">
-        <v>1.945254019625723</v>
+        <v>2.422785890282305</v>
       </c>
       <c r="P19" t="n">
-        <v>3.167951486727213</v>
+        <v>2.664907120557442</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.040822381314439</v>
+        <v>1.828080591028004</v>
       </c>
       <c r="R19" t="n">
-        <v>5.091657489665412</v>
+        <v>1.703391216244606</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.496660405031012</v>
+        <v>1.730840912620108</v>
       </c>
       <c r="U19" t="n">
-        <v>1.855284946833723</v>
+        <v>1.907105190260129</v>
       </c>
       <c r="V19" t="n">
-        <v>2.374541228130727</v>
+        <v>1.948513689843567</v>
       </c>
       <c r="W19" t="n">
-        <v>2.810002181618042</v>
+        <v>2.272597925576918</v>
       </c>
       <c r="X19" t="n">
-        <v>1.525359114481463</v>
+        <v>0.5577519416770899</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.49899264612916</v>
+        <v>3.470518447932268</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.825613498596399</v>
+        <v>2.442277518121108</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.747715680068001</v>
+        <v>1.51699489304905</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.97999942600135</v>
+        <v>1.986475556053547</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.889985867870162</v>
+        <v>1.464475611726454</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.695227897245297</v>
+        <v>1.989972000246785</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.928731800700181</v>
+        <v>1.80339860746935</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.954794562040666</v>
+        <v>2.07443524777963</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.403136351395824</v>
+        <v>2.229149271491141</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.970544831926039</v>
+        <v>3.482294240734142</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.903059469401551</v>
+        <v>2.272972852951041</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.762166565735673</v>
+        <v>2.084599441822351</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.847681602682102</v>
+        <v>3.79151542620836</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.391433648792235</v>
+        <v>1.524058883282909</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.919487522089702</v>
+        <v>1.9267396034744</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.77735390263312</v>
+        <v>1.975336564400672</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.404330028705971</v>
+        <v>1.840793077080721</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.921488570739536</v>
+        <v>4.411017515933349</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.336052700006867</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.558679069686868</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.615216712377542</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.807786718308561</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.403340427862094</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.497844181046533</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.9614911180200391</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.523067504987589</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.441130313806064</v>
+        <v>1.807842688350391</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.014693514735531</v>
+        <v>3.642660933086359</v>
       </c>
       <c r="C20" t="n">
-        <v>3.261512019564386</v>
+        <v>1.902833359204842</v>
       </c>
       <c r="D20" t="n">
-        <v>3.468513421473021</v>
+        <v>1.60528966651714</v>
       </c>
       <c r="E20" t="n">
-        <v>2.432943259423464</v>
+        <v>4.016650445073632</v>
       </c>
       <c r="F20" t="n">
-        <v>2.279126021744746</v>
+        <v>3.153274497577071</v>
       </c>
       <c r="G20" t="n">
-        <v>3.605031550094983</v>
+        <v>1.308187751445476</v>
       </c>
       <c r="H20" t="n">
-        <v>2.233145310441734</v>
+        <v>5.643062360230497</v>
       </c>
       <c r="I20" t="n">
-        <v>4.266264920602186</v>
+        <v>3.873833390712622</v>
       </c>
       <c r="J20" t="n">
-        <v>3.04501823590418</v>
+        <v>3.642416052537267</v>
       </c>
       <c r="K20" t="n">
-        <v>3.664103233316918</v>
+        <v>2.042204827999064</v>
       </c>
       <c r="L20" t="n">
-        <v>3.221066958330669</v>
+        <v>2.314454333743118</v>
       </c>
       <c r="M20" t="n">
-        <v>6.19064998575367</v>
+        <v>1.828446235664499</v>
       </c>
       <c r="N20" t="n">
-        <v>4.902913330508494</v>
+        <v>3.600016083724037</v>
       </c>
       <c r="O20" t="n">
-        <v>3.475126179548313</v>
+        <v>1.375980026380142</v>
       </c>
       <c r="P20" t="n">
-        <v>4.233203844516392</v>
+        <v>3.36200238561123</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.70240440238952</v>
+        <v>2.714056297736276</v>
       </c>
       <c r="R20" t="n">
-        <v>6.352034734958242</v>
+        <v>2.333175474378257</v>
       </c>
       <c r="S20" t="n">
-        <v>2.496660405031012</v>
+        <v>1.730840912620108</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.423904107923168</v>
+        <v>2.833871871653276</v>
       </c>
       <c r="V20" t="n">
-        <v>3.495840387409269</v>
+        <v>1.290626114215583</v>
       </c>
       <c r="W20" t="n">
-        <v>4.881072243281761</v>
+        <v>1.086113868910313</v>
       </c>
       <c r="X20" t="n">
-        <v>3.521545673386837</v>
+        <v>1.599877315695928</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.168704775495917</v>
+        <v>3.793685389173459</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.216379410976053</v>
+        <v>3.123310562461029</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.909330446331095</v>
+        <v>2.207291068378748</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.002728182612439</v>
+        <v>2.519265683366507</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.397969441784813</v>
+        <v>1.853673076305023</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.941388758687628</v>
+        <v>2.802134102145604</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.575440025513434</v>
+        <v>2.22237569092704</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.889329174287273</v>
+        <v>2.12974565314225</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.483362721516619</v>
+        <v>2.611870328829557</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.205425129064021</v>
+        <v>4.254125897818796</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.015157493427473</v>
+        <v>1.927707759975827</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.992067020703459</v>
+        <v>2.319609917060998</v>
       </c>
       <c r="AK20" t="n">
-        <v>4.20453561432382</v>
+        <v>4.360053046252661</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.741188086128129</v>
+        <v>2.024459766586453</v>
       </c>
       <c r="AM20" t="n">
-        <v>3.761730663304094</v>
+        <v>2.66559895881958</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.126700726937258</v>
+        <v>2.896342852694319</v>
       </c>
       <c r="AO20" t="n">
-        <v>3.764359279063907</v>
+        <v>2.64096820772565</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.286366781775484</v>
+        <v>3.792542595319389</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.660457914479184</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>3.933873998650396</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.621481158480967</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.146784204430781</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.705960024269339</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.474373492432314</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>3.139423755345609</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>3.803110661137406</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4.154304383797016</v>
+        <v>2.450437221308105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.201458368442583</v>
+        <v>3.237580104669461</v>
       </c>
       <c r="C21" t="n">
-        <v>2.600364923599682</v>
+        <v>2.240045327400948</v>
       </c>
       <c r="D21" t="n">
-        <v>3.328827573375952</v>
+        <v>2.628905740198753</v>
       </c>
       <c r="E21" t="n">
-        <v>1.976228974368941</v>
+        <v>4.296279356489823</v>
       </c>
       <c r="F21" t="n">
-        <v>3.483067607794611</v>
+        <v>4.382668424198251</v>
       </c>
       <c r="G21" t="n">
-        <v>3.490534101589233</v>
+        <v>3.839064827839247</v>
       </c>
       <c r="H21" t="n">
-        <v>3.586936510874631</v>
+        <v>7.09784035478546</v>
       </c>
       <c r="I21" t="n">
-        <v>5.556835650412341</v>
+        <v>4.142346170889593</v>
       </c>
       <c r="J21" t="n">
-        <v>4.129663439467472</v>
+        <v>1.316767286023679</v>
       </c>
       <c r="K21" t="n">
-        <v>2.626094417885938</v>
+        <v>2.06798192949132</v>
       </c>
       <c r="L21" t="n">
-        <v>2.167610816842021</v>
+        <v>2.912771168361388</v>
       </c>
       <c r="M21" t="n">
-        <v>6.810758635976678</v>
+        <v>1.986638321013243</v>
       </c>
       <c r="N21" t="n">
-        <v>4.300996576945037</v>
+        <v>1.76912768292787</v>
       </c>
       <c r="O21" t="n">
-        <v>3.112820443753023</v>
+        <v>2.9343221846754</v>
       </c>
       <c r="P21" t="n">
-        <v>3.459181748944077</v>
+        <v>1.031645237471527</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.562122834496294</v>
+        <v>2.724063217597378</v>
       </c>
       <c r="R21" t="n">
-        <v>3.88096710127998</v>
+        <v>3.401985219377492</v>
       </c>
       <c r="S21" t="n">
-        <v>1.855284946833723</v>
+        <v>1.907105190260129</v>
       </c>
       <c r="T21" t="n">
-        <v>3.423904107923168</v>
+        <v>2.833871871653276</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>2.222566340556051</v>
+        <v>2.634911064187538</v>
       </c>
       <c r="W21" t="n">
-        <v>2.604483962408884</v>
+        <v>2.833348194998908</v>
       </c>
       <c r="X21" t="n">
-        <v>2.177319492109687</v>
+        <v>1.934912926415042</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.860095040112625</v>
+        <v>1.821039840168808</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.418151902978804</v>
+        <v>0.9678812166602178</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.939720350324765</v>
+        <v>0.8961920843240929</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.452889713255554</v>
+        <v>0.8510532614863946</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.099937156372622</v>
+        <v>1.114118570859214</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.461036090872295</v>
+        <v>0.3906871579912007</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.552745294161307</v>
+        <v>1.031309073271962</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.972767629166409</v>
+        <v>1.320084206933019</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.069215916393971</v>
+        <v>1.138000411953126</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.591228634763765</v>
+        <v>3.091969985724856</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.662209386753143</v>
+        <v>1.887891010445718</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.279202173088249</v>
+        <v>1.34526473591448</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.100785993415658</v>
+        <v>3.445195361182615</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.451386540067586</v>
+        <v>1.048920842860947</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.778921879230911</v>
+        <v>0.7608548744314158</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.998583159107221</v>
+        <v>0.501286644709706</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.387013398405951</v>
+        <v>0.7117059902199535</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.869227887668818</v>
+        <v>4.233586579737097</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.589997084314835</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.066030010115374</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.562500257895514</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.292599625273194</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.792453605378375</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.758027223947439</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.656701691051205</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>2.153595069654111</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>2.682300912645847</v>
+        <v>1.013628562022854</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.803455384227065</v>
+        <v>3.17617632885335</v>
       </c>
       <c r="C22" t="n">
-        <v>2.982538788559493</v>
+        <v>2.41417477166351</v>
       </c>
       <c r="D22" t="n">
-        <v>2.846858786269695</v>
+        <v>1.909960645452956</v>
       </c>
       <c r="E22" t="n">
-        <v>2.969539764767302</v>
+        <v>4.250438239422761</v>
       </c>
       <c r="F22" t="n">
-        <v>2.883579824786041</v>
+        <v>3.666013456301735</v>
       </c>
       <c r="G22" t="n">
-        <v>1.441523728780205</v>
+        <v>2.387334419996338</v>
       </c>
       <c r="H22" t="n">
-        <v>2.723277672747324</v>
+        <v>5.858416954628398</v>
       </c>
       <c r="I22" t="n">
-        <v>4.80523964987207</v>
+        <v>4.559550053490721</v>
       </c>
       <c r="J22" t="n">
-        <v>2.691612763420557</v>
+        <v>3.481664489017313</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8943140807148786</v>
+        <v>2.435385985879542</v>
       </c>
       <c r="L22" t="n">
-        <v>1.388915263277528</v>
+        <v>2.22695207720663</v>
       </c>
       <c r="M22" t="n">
-        <v>6.518351771969902</v>
+        <v>2.167381160815836</v>
       </c>
       <c r="N22" t="n">
-        <v>4.299046216962889</v>
+        <v>3.76875652204903</v>
       </c>
       <c r="O22" t="n">
-        <v>2.311425886491544</v>
+        <v>2.357278841502209</v>
       </c>
       <c r="P22" t="n">
-        <v>2.846609418540874</v>
+        <v>3.03776669666784</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.037970795194373</v>
+        <v>3.150853914414793</v>
       </c>
       <c r="R22" t="n">
-        <v>3.460590487408037</v>
+        <v>2.610265350633689</v>
       </c>
       <c r="S22" t="n">
-        <v>2.374541228130727</v>
+        <v>1.948513689843567</v>
       </c>
       <c r="T22" t="n">
-        <v>3.495840387409269</v>
+        <v>1.290626114215583</v>
       </c>
       <c r="U22" t="n">
-        <v>2.222566340556051</v>
+        <v>2.634911064187538</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.054027606586587</v>
+        <v>0.6877162965421648</v>
       </c>
       <c r="X22" t="n">
-        <v>2.792889716438993</v>
+        <v>2.051967297098116</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.440470845254703</v>
+        <v>3.278696903974147</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.399099507037946</v>
+        <v>2.868796107275253</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.476857000548318</v>
+        <v>2.208296131368491</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.167685432772768</v>
+        <v>2.043314613516642</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.099989230047281</v>
+        <v>1.963279705940216</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.543550425036059</v>
+        <v>2.596747127162128</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.67337182178162</v>
+        <v>2.048449193873574</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.217359389673586</v>
+        <v>2.202719001257997</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.536773397835975</v>
+        <v>2.608659445446385</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.201127517626403</v>
+        <v>4.551372912195271</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.120166706903084</v>
+        <v>1.343837780869456</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.885016932022149</v>
+        <v>2.587783401559939</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.906201989631552</v>
+        <v>4.360218905562918</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.926291745759881</v>
+        <v>2.030556778183251</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.90966180652548</v>
+        <v>2.563287015052407</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.90101552721031</v>
+        <v>2.686134287960026</v>
       </c>
       <c r="AO22" t="n">
-        <v>2.383415651154893</v>
+        <v>2.334113493634191</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.551477565627547</v>
+        <v>2.666426507809103</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.644438671140047</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.806850904951221</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.848818325238063</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.240744994208669</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.962435918110109</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.390530442611282</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.77576214051689</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>2.473053537077742</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.928845773350701</v>
+        <v>2.217234269971782</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.670733770460223</v>
+        <v>3.089182413808422</v>
       </c>
       <c r="C23" t="n">
-        <v>2.425075598878268</v>
+        <v>2.288434604335202</v>
       </c>
       <c r="D23" t="n">
-        <v>2.943050046746678</v>
+        <v>1.707244891185492</v>
       </c>
       <c r="E23" t="n">
-        <v>3.240287238562521</v>
+        <v>3.872741188816127</v>
       </c>
       <c r="F23" t="n">
-        <v>4.415312640899345</v>
+        <v>3.10114269757289</v>
       </c>
       <c r="G23" t="n">
-        <v>4.059144076668352</v>
+        <v>1.952015516155588</v>
       </c>
       <c r="H23" t="n">
-        <v>4.533981660583268</v>
+        <v>5.352936798788527</v>
       </c>
       <c r="I23" t="n">
-        <v>6.083188409934844</v>
+        <v>4.319803761504795</v>
       </c>
       <c r="J23" t="n">
-        <v>4.44338321270518</v>
+        <v>3.607977559875814</v>
       </c>
       <c r="K23" t="n">
-        <v>3.341116236861381</v>
+        <v>2.187106533903827</v>
       </c>
       <c r="L23" t="n">
-        <v>3.734071361810348</v>
+        <v>1.826299159325883</v>
       </c>
       <c r="M23" t="n">
-        <v>5.467695147422264</v>
+        <v>1.946376213744655</v>
       </c>
       <c r="N23" t="n">
-        <v>2.508119689265302</v>
+        <v>3.712180442669688</v>
       </c>
       <c r="O23" t="n">
-        <v>2.490489250186267</v>
+        <v>1.952953062752409</v>
       </c>
       <c r="P23" t="n">
-        <v>3.570893730134001</v>
+        <v>3.211177472408056</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.55198958886447</v>
+        <v>3.329691554986308</v>
       </c>
       <c r="R23" t="n">
-        <v>3.558271115439733</v>
+        <v>2.972542298694829</v>
       </c>
       <c r="S23" t="n">
-        <v>2.810002181618042</v>
+        <v>2.272597925576918</v>
       </c>
       <c r="T23" t="n">
-        <v>4.881072243281761</v>
+        <v>1.086113868910313</v>
       </c>
       <c r="U23" t="n">
-        <v>2.604483962408884</v>
+        <v>2.833348194998908</v>
       </c>
       <c r="V23" t="n">
-        <v>3.054027606586587</v>
+        <v>0.6877162965421648</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.57440053235314</v>
+        <v>2.234267125427342</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.082708530262314</v>
+        <v>3.346693315169516</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.980596057377805</v>
+        <v>2.974309035360408</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.66774713690269</v>
+        <v>2.359792312856756</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.60707545365335</v>
+        <v>2.262185527849229</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.184609646588556</v>
+        <v>2.000369110542267</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.490464037511712</v>
+        <v>2.755759676279142</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.995525310214713</v>
+        <v>2.140103936027708</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.065317779235284</v>
+        <v>2.086432571116173</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.80020099704855</v>
+        <v>2.566664975903326</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.754724670414315</v>
+        <v>4.604112478272261</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.786962755323623</v>
+        <v>1.337640773906595</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.617466565675103</v>
+        <v>2.465771099907084</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.837166229006027</v>
+        <v>4.521979265228896</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.232055033042219</v>
+        <v>2.112780266108095</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.766545425676303</v>
+        <v>2.686744680475955</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.861924924396287</v>
+        <v>2.910405390271638</v>
       </c>
       <c r="AO23" t="n">
-        <v>2.138000870648754</v>
+        <v>2.576529728278102</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.354606360765603</v>
+        <v>2.729128295699009</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.551568904218874</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.930040518075831</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.086991161730877</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.670858128461325</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.120412609380144</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.347214936333498</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.060127529909015</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.847560674375352</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.924437807003848</v>
+        <v>2.386111633477983</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.740277316576763</v>
+        <v>3.607481714435003</v>
       </c>
       <c r="C24" t="n">
-        <v>1.28251346472269</v>
+        <v>2.086902467743083</v>
       </c>
       <c r="D24" t="n">
-        <v>1.97333565910917</v>
+        <v>2.386810025024726</v>
       </c>
       <c r="E24" t="n">
-        <v>1.926047905706113</v>
+        <v>4.185893245377583</v>
       </c>
       <c r="F24" t="n">
-        <v>3.433097216607355</v>
+        <v>3.926299623559333</v>
       </c>
       <c r="G24" t="n">
-        <v>3.702436667363802</v>
+        <v>2.564464330067904</v>
       </c>
       <c r="H24" t="n">
-        <v>3.423984788396662</v>
+        <v>6.730005415120139</v>
       </c>
       <c r="I24" t="n">
-        <v>5.528732761582249</v>
+        <v>3.681477373434011</v>
       </c>
       <c r="J24" t="n">
-        <v>3.513191740352305</v>
+        <v>2.985479845391986</v>
       </c>
       <c r="K24" t="n">
-        <v>2.976528239016756</v>
+        <v>2.22910208376958</v>
       </c>
       <c r="L24" t="n">
-        <v>3.360643081064129</v>
+        <v>3.14082756394611</v>
       </c>
       <c r="M24" t="n">
-        <v>5.097440685247632</v>
+        <v>2.1139740185436</v>
       </c>
       <c r="N24" t="n">
-        <v>2.252596378381573</v>
+        <v>2.979291097370234</v>
       </c>
       <c r="O24" t="n">
-        <v>1.755762064262472</v>
+        <v>2.192134524547235</v>
       </c>
       <c r="P24" t="n">
-        <v>3.452259482510446</v>
+        <v>2.769032761183354</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.265484463217816</v>
+        <v>2.018265707127957</v>
       </c>
       <c r="R24" t="n">
-        <v>4.533758219583625</v>
+        <v>2.074986517129707</v>
       </c>
       <c r="S24" t="n">
-        <v>1.525359114481463</v>
+        <v>0.5577519416770899</v>
       </c>
       <c r="T24" t="n">
-        <v>3.521545673386837</v>
+        <v>1.599877315695928</v>
       </c>
       <c r="U24" t="n">
-        <v>2.177319492109687</v>
+        <v>1.934912926415042</v>
       </c>
       <c r="V24" t="n">
-        <v>2.792889716438993</v>
+        <v>2.051967297098116</v>
       </c>
       <c r="W24" t="n">
-        <v>1.57440053235314</v>
+        <v>2.234267125427342</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.267968340278684</v>
+        <v>3.469705148225568</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.723370679754065</v>
+        <v>2.314444189830276</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.139050499841315</v>
+        <v>1.579050732877015</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.311475327007579</v>
+        <v>2.067323717289844</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.819689425789039</v>
+        <v>1.396382671794669</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.149201617368112</v>
+        <v>1.933977389301806</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.078696262733853</v>
+        <v>1.660169721173468</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.638522227040172</v>
+        <v>1.830923945617742</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.190745776101511</v>
+        <v>2.054513269354043</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.314537726987675</v>
+        <v>3.549818405532627</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.9188486117249713</v>
+        <v>2.294151908225823</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.8817091708855901</v>
+        <v>1.810277455078494</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.386619436505264</v>
+        <v>4.091036465966348</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.238363747274376</v>
+        <v>1.333421114471073</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.7924024715186906</v>
+        <v>1.776456766970755</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.352080550989854</v>
+        <v>2.043767400403246</v>
       </c>
       <c r="AO24" t="n">
-        <v>1.442404178076632</v>
+        <v>1.877379457799754</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.628277106346315</v>
+        <v>4.503741960682847</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.688622068262221</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.215747719369396</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.553172504197522</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.50669832872713</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.480000920221219</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.415390324570892</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.194655329616539</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.114816913338288</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>3.680715148047694</v>
+        <v>1.684423865721694</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.72402322859211</v>
+        <v>2.904064855518503</v>
       </c>
       <c r="C25" t="n">
-        <v>2.631088009705586</v>
+        <v>2.971860946441493</v>
       </c>
       <c r="D25" t="n">
-        <v>2.90203541163467</v>
+        <v>3.098437832915537</v>
       </c>
       <c r="E25" t="n">
-        <v>3.45880760671696</v>
+        <v>4.15926879295812</v>
       </c>
       <c r="F25" t="n">
-        <v>4.752968139252077</v>
+        <v>4.375332549111667</v>
       </c>
       <c r="G25" t="n">
-        <v>5.966567912468372</v>
+        <v>4.585801267519794</v>
       </c>
       <c r="H25" t="n">
-        <v>4.600601517862083</v>
+        <v>7.301756158817837</v>
       </c>
       <c r="I25" t="n">
-        <v>7.102422969888434</v>
+        <v>5.34157201749376</v>
       </c>
       <c r="J25" t="n">
-        <v>4.851602761217847</v>
+        <v>1.722586400366974</v>
       </c>
       <c r="K25" t="n">
-        <v>5.402438486171206</v>
+        <v>2.486562579283467</v>
       </c>
       <c r="L25" t="n">
-        <v>5.841297356117646</v>
+        <v>2.60739051575959</v>
       </c>
       <c r="M25" t="n">
-        <v>6.295664964291414</v>
+        <v>2.522942024583733</v>
       </c>
       <c r="N25" t="n">
-        <v>3.707993736174576</v>
+        <v>2.4998073280934</v>
       </c>
       <c r="O25" t="n">
-        <v>3.621503895821529</v>
+        <v>3.743225696081289</v>
       </c>
       <c r="P25" t="n">
-        <v>4.977622992833588</v>
+        <v>1.305597074361694</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.102079342174751</v>
+        <v>4.368700818642172</v>
       </c>
       <c r="R25" t="n">
-        <v>7.529733061097079</v>
+        <v>4.887703937921181</v>
       </c>
       <c r="S25" t="n">
-        <v>3.49899264612916</v>
+        <v>3.470518447932268</v>
       </c>
       <c r="T25" t="n">
-        <v>5.168704775495917</v>
+        <v>3.793685389173459</v>
       </c>
       <c r="U25" t="n">
-        <v>4.860095040112625</v>
+        <v>1.821039840168808</v>
       </c>
       <c r="V25" t="n">
-        <v>5.440470845254703</v>
+        <v>3.278696903974147</v>
       </c>
       <c r="W25" t="n">
-        <v>4.082708530262314</v>
+        <v>3.346693315169516</v>
       </c>
       <c r="X25" t="n">
-        <v>3.267968340278684</v>
+        <v>3.469705148225568</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.424979905128739</v>
+        <v>1.719760035863114</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.803670738983532</v>
+        <v>2.193939741746028</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.883403515663372</v>
+        <v>1.524548666569665</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.639144151829211</v>
+        <v>2.380805525961052</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.820254114661104</v>
+        <v>1.74580666084289</v>
       </c>
       <c r="AE25" t="n">
-        <v>3.827711372698106</v>
+        <v>1.895406641246565</v>
       </c>
       <c r="AF25" t="n">
-        <v>4.31796442107603</v>
+        <v>2.028445415739116</v>
       </c>
       <c r="AG25" t="n">
-        <v>5.137669757690254</v>
+        <v>2.120556849807095</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.145718052748702</v>
+        <v>4.34616128245009</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.046874787929621</v>
+        <v>2.047208266268132</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.275644796750353</v>
+        <v>2.38290396617161</v>
       </c>
       <c r="AK25" t="n">
-        <v>3.439178399731049</v>
+        <v>4.177973689488202</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.819688980830223</v>
+        <v>2.199400714418817</v>
       </c>
       <c r="AM25" t="n">
-        <v>3.26238336512733</v>
+        <v>1.90560712104736</v>
       </c>
       <c r="AN25" t="n">
-        <v>3.449322249500447</v>
+        <v>1.740725903627074</v>
       </c>
       <c r="AO25" t="n">
-        <v>3.183629865425844</v>
+        <v>1.724786020911638</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.271290737880581</v>
+        <v>3.774884013842722</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.931699337477177</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>3.271513490288398</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.498659090140482</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.540357240079344</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.303456172434698</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.244986349059971</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>3.790710460936306</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>3.442009176065232</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>5.591926167399</v>
+        <v>1.973142966349604</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.792817147489536</v>
+        <v>2.498133994507744</v>
       </c>
       <c r="C26" t="n">
-        <v>1.712342499363907</v>
+        <v>2.822129654309585</v>
       </c>
       <c r="D26" t="n">
-        <v>1.722800896034085</v>
+        <v>3.127964619195395</v>
       </c>
       <c r="E26" t="n">
-        <v>2.348662190685007</v>
+        <v>3.665558987370673</v>
       </c>
       <c r="F26" t="n">
-        <v>3.501925217648454</v>
+        <v>4.079944703497924</v>
       </c>
       <c r="G26" t="n">
-        <v>3.335623437290228</v>
+        <v>4.020270031740368</v>
       </c>
       <c r="H26" t="n">
-        <v>3.224465885533756</v>
+        <v>6.981037873740062</v>
       </c>
       <c r="I26" t="n">
-        <v>5.992049691765914</v>
+        <v>4.189699462825562</v>
       </c>
       <c r="J26" t="n">
-        <v>3.271011465656105</v>
+        <v>1.953129612859077</v>
       </c>
       <c r="K26" t="n">
-        <v>2.358062068043995</v>
+        <v>2.364480266608161</v>
       </c>
       <c r="L26" t="n">
-        <v>3.151362940337099</v>
+        <v>3.014098238668193</v>
       </c>
       <c r="M26" t="n">
-        <v>6.373411518212655</v>
+        <v>2.389632169242796</v>
       </c>
       <c r="N26" t="n">
-        <v>3.321100744364195</v>
+        <v>2.065356390802723</v>
       </c>
       <c r="O26" t="n">
-        <v>1.799840653809223</v>
+        <v>3.262132182385281</v>
       </c>
       <c r="P26" t="n">
-        <v>3.152651743429274</v>
+        <v>1.642340695738873</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.847887952560944</v>
+        <v>3.379813664111801</v>
       </c>
       <c r="R26" t="n">
-        <v>4.48914804852778</v>
+        <v>4.038217935741987</v>
       </c>
       <c r="S26" t="n">
-        <v>1.825613498596399</v>
+        <v>2.442277518121108</v>
       </c>
       <c r="T26" t="n">
-        <v>4.216379410976053</v>
+        <v>3.123310562461029</v>
       </c>
       <c r="U26" t="n">
-        <v>2.418151902978804</v>
+        <v>0.9678812166602178</v>
       </c>
       <c r="V26" t="n">
-        <v>2.399099507037946</v>
+        <v>2.868796107275253</v>
       </c>
       <c r="W26" t="n">
-        <v>1.980596057377805</v>
+        <v>2.974309035360408</v>
       </c>
       <c r="X26" t="n">
-        <v>1.723370679754065</v>
+        <v>2.314444189830276</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.424979905128739</v>
+        <v>1.719760035863114</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.370960889073348</v>
+        <v>1.685907852885719</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.23570159048949</v>
+        <v>1.272343133019207</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.824887779508069</v>
+        <v>1.610670237078058</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.439390781019609</v>
+        <v>0.6202408047879713</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.028881108125789</v>
+        <v>1.065575150952187</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.658786534611409</v>
+        <v>1.268597919004157</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.890103319918011</v>
+        <v>1.022494043953063</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.896906746255839</v>
+        <v>3.615070001277931</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.578980998226942</v>
+        <v>2.088374640685719</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.367179885740202</v>
+        <v>1.381080777713996</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.236718990720947</v>
+        <v>4.296629434147268</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.138296376896564</v>
+        <v>1.227422419927771</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.80170471406718</v>
+        <v>0.744327567336437</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.298840786954081</v>
+        <v>1.297227315717864</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.550073945758242</v>
+        <v>1.189962245511973</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.401317374410673</v>
+        <v>4.07085075763876</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.883189371833949</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.146009621531414</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.051825480488616</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0.3882320636365378</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>1.131791027809913</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.248569224014129</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.231093030810275</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.019177259490367</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>4.176663893563307</v>
+        <v>0.9520055043436831</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.319763038761456</v>
+        <v>3.541358357664106</v>
       </c>
       <c r="C27" t="n">
-        <v>2.021924490188854</v>
+        <v>1.405997148221669</v>
       </c>
       <c r="D27" t="n">
-        <v>2.30378626916921</v>
+        <v>1.821525735531988</v>
       </c>
       <c r="E27" t="n">
-        <v>2.205946154392611</v>
+        <v>4.346525737732648</v>
       </c>
       <c r="F27" t="n">
-        <v>3.911004843894611</v>
+        <v>4.074616923241772</v>
       </c>
       <c r="G27" t="n">
-        <v>3.650538777015433</v>
+        <v>3.182989864591978</v>
       </c>
       <c r="H27" t="n">
-        <v>3.631110254341277</v>
+        <v>6.801642469285817</v>
       </c>
       <c r="I27" t="n">
-        <v>6.213738381886453</v>
+        <v>4.027912597433565</v>
       </c>
       <c r="J27" t="n">
-        <v>3.610349913303997</v>
+        <v>1.503654323823777</v>
       </c>
       <c r="K27" t="n">
-        <v>2.433077020971826</v>
+        <v>1.480944658658535</v>
       </c>
       <c r="L27" t="n">
-        <v>3.293487509045081</v>
+        <v>2.439253529491793</v>
       </c>
       <c r="M27" t="n">
-        <v>5.778935326976851</v>
+        <v>1.302130325154512</v>
       </c>
       <c r="N27" t="n">
-        <v>2.847850681126513</v>
+        <v>1.925727477563713</v>
       </c>
       <c r="O27" t="n">
-        <v>2.101473039413135</v>
+        <v>2.226364082098928</v>
       </c>
       <c r="P27" t="n">
-        <v>3.889581182457428</v>
+        <v>1.284301449746412</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.589165118568488</v>
+        <v>2.354305965065915</v>
       </c>
       <c r="R27" t="n">
-        <v>4.123134129991026</v>
+        <v>2.880674854414857</v>
       </c>
       <c r="S27" t="n">
-        <v>1.747715680068001</v>
+        <v>1.51699489304905</v>
       </c>
       <c r="T27" t="n">
-        <v>3.909330446331095</v>
+        <v>2.207291068378748</v>
       </c>
       <c r="U27" t="n">
-        <v>1.939720350324765</v>
+        <v>0.8961920843240929</v>
       </c>
       <c r="V27" t="n">
-        <v>2.476857000548318</v>
+        <v>2.208296131368491</v>
       </c>
       <c r="W27" t="n">
-        <v>1.66774713690269</v>
+        <v>2.359792312856756</v>
       </c>
       <c r="X27" t="n">
-        <v>1.139050499841315</v>
+        <v>1.579050732877015</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.803670738983532</v>
+        <v>2.193939741746028</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.370960889073348</v>
+        <v>1.685907852885719</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.9209005314475021</v>
+        <v>0.966541616988298</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.690952893418824</v>
+        <v>0.658527617824044</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.7794920348125159</v>
+        <v>1.100771406951136</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.071205961412449</v>
+        <v>1.105256468305269</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.6203366648858754</v>
+        <v>1.241517042633105</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.694362720716827</v>
+        <v>1.41911542166559</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.812823171041951</v>
+        <v>3.070144219468097</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.9384836696475081</v>
+        <v>1.551798881974777</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.5726766816071727</v>
+        <v>1.314378832387651</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.6837423822935208</v>
+        <v>3.078637719374058</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.118631882430354</v>
+        <v>0.9692908597764655</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.259535587634105</v>
+        <v>1.192252123050213</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.6986866399877142</v>
+        <v>0.8315221075835265</v>
       </c>
       <c r="AO27" t="n">
-        <v>1.274214875767389</v>
+        <v>0.9463818807555641</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.687198053894617</v>
+        <v>4.192795891314408</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.605061475773355</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.6923819011705493</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.888009067097615</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.26616952624539</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.534166072295377</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>1.490719641084378</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.178060765344452</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0.5150434747615754</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>4.147203818301882</v>
+        <v>1.291879624048919</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.561092972636197</v>
+        <v>2.887813106443401</v>
       </c>
       <c r="C28" t="n">
-        <v>1.99735272711632</v>
+        <v>2.084402878076655</v>
       </c>
       <c r="D28" t="n">
-        <v>1.874334651110356</v>
+        <v>2.198125112596649</v>
       </c>
       <c r="E28" t="n">
-        <v>2.617327097903438</v>
+        <v>4.136387204778456</v>
       </c>
       <c r="F28" t="n">
-        <v>3.674429544202387</v>
+        <v>4.082381798732816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.11643807103719</v>
+        <v>3.547372022106673</v>
       </c>
       <c r="H28" t="n">
-        <v>3.381203173289457</v>
+        <v>6.813573293419953</v>
       </c>
       <c r="I28" t="n">
-        <v>5.837747623489021</v>
+        <v>4.498981301902102</v>
       </c>
       <c r="J28" t="n">
-        <v>3.080244528930492</v>
+        <v>1.628855600792143</v>
       </c>
       <c r="K28" t="n">
-        <v>2.106679267555619</v>
+        <v>1.868860005552528</v>
       </c>
       <c r="L28" t="n">
-        <v>3.204147411820375</v>
+        <v>2.311661838158102</v>
       </c>
       <c r="M28" t="n">
-        <v>5.401121340102708</v>
+        <v>1.733084442749497</v>
       </c>
       <c r="N28" t="n">
-        <v>2.50803919211305</v>
+        <v>2.276179443856344</v>
       </c>
       <c r="O28" t="n">
-        <v>1.415870512949522</v>
+        <v>2.777954848334646</v>
       </c>
       <c r="P28" t="n">
-        <v>3.515934524714113</v>
+        <v>1.0979120544735</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.222383074563708</v>
+        <v>3.048906792428466</v>
       </c>
       <c r="R28" t="n">
-        <v>3.964284135006604</v>
+        <v>3.383797829415955</v>
       </c>
       <c r="S28" t="n">
-        <v>1.97999942600135</v>
+        <v>1.986475556053547</v>
       </c>
       <c r="T28" t="n">
-        <v>4.002728182612439</v>
+        <v>2.519265683366507</v>
       </c>
       <c r="U28" t="n">
-        <v>2.452889713255554</v>
+        <v>0.8510532614863946</v>
       </c>
       <c r="V28" t="n">
-        <v>2.167685432772768</v>
+        <v>2.043314613516642</v>
       </c>
       <c r="W28" t="n">
-        <v>1.60707545365335</v>
+        <v>2.262185527849229</v>
       </c>
       <c r="X28" t="n">
-        <v>1.311475327007579</v>
+        <v>2.067323717289844</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.883403515663372</v>
+        <v>1.524548666569665</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.23570159048949</v>
+        <v>1.272343133019207</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.9209005314475021</v>
+        <v>0.966541616988298</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.229469301682938</v>
+        <v>1.135505609740307</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.423388822000337</v>
+        <v>0.8716465186174606</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.042403317953217</v>
+        <v>0.8475752109817781</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.056513308317701</v>
+        <v>1.237931698513108</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.089109494262575</v>
+        <v>1.40380071673294</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.04441080433856</v>
+        <v>3.636528494668117</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.163296086353139</v>
+        <v>1.150645414238359</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.068669086905067</v>
+        <v>1.598745624224217</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.383397300425969</v>
+        <v>3.575312943549963</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.404940865653469</v>
+        <v>1.039784115027303</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.051510405487078</v>
+        <v>1.061225236291691</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.448707732716423</v>
+        <v>0.8491831394321234</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.15233521719633</v>
+        <v>0.6281803712175099</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.979499971665102</v>
+        <v>3.474289573655004</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.571969341343863</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.318984653068658</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.789799587511845</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>1.02119418666207</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.289190274753421</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.057710455255011</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.182472966576926</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.8356208253508683</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>4.413564924658966</v>
+        <v>0.9669988387291477</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.953268445221083</v>
+        <v>3.299803636737129</v>
       </c>
       <c r="C29" t="n">
-        <v>2.230133515311165</v>
+        <v>1.489735839926417</v>
       </c>
       <c r="D29" t="n">
-        <v>2.163850902206323</v>
+        <v>1.773812049202641</v>
       </c>
       <c r="E29" t="n">
-        <v>2.569475683494677</v>
+        <v>4.034386795475451</v>
       </c>
       <c r="F29" t="n">
-        <v>2.921385207027513</v>
+        <v>3.715875225306229</v>
       </c>
       <c r="G29" t="n">
-        <v>2.04463739715662</v>
+        <v>2.849847827008579</v>
       </c>
       <c r="H29" t="n">
-        <v>2.799044760272983</v>
+        <v>6.225041198818355</v>
       </c>
       <c r="I29" t="n">
-        <v>4.880199398613457</v>
+        <v>3.512109151691662</v>
       </c>
       <c r="J29" t="n">
-        <v>2.616445191819501</v>
+        <v>1.901754225476539</v>
       </c>
       <c r="K29" t="n">
-        <v>1.416962878774546</v>
+        <v>1.399670788864011</v>
       </c>
       <c r="L29" t="n">
-        <v>2.119386695982672</v>
+        <v>2.28818481653365</v>
       </c>
       <c r="M29" t="n">
-        <v>5.603326876996629</v>
+        <v>1.173906885366403</v>
       </c>
       <c r="N29" t="n">
-        <v>3.207892843921848</v>
+        <v>1.89035914417505</v>
       </c>
       <c r="O29" t="n">
-        <v>1.472695237202685</v>
+        <v>1.870390769565178</v>
       </c>
       <c r="P29" t="n">
-        <v>2.842981414988542</v>
+        <v>1.698449660304101</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.741271340028113</v>
+        <v>2.220558317391023</v>
       </c>
       <c r="R29" t="n">
-        <v>3.548134739014785</v>
+        <v>2.828332132066314</v>
       </c>
       <c r="S29" t="n">
-        <v>1.889985867870162</v>
+        <v>1.464475611726454</v>
       </c>
       <c r="T29" t="n">
-        <v>3.397969441784813</v>
+        <v>1.853673076305023</v>
       </c>
       <c r="U29" t="n">
-        <v>2.099937156372622</v>
+        <v>1.114118570859214</v>
       </c>
       <c r="V29" t="n">
-        <v>1.099989230047281</v>
+        <v>1.963279705940216</v>
       </c>
       <c r="W29" t="n">
-        <v>2.184609646588556</v>
+        <v>2.000369110542267</v>
       </c>
       <c r="X29" t="n">
-        <v>1.819689425789039</v>
+        <v>1.396382671794669</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.639144151829211</v>
+        <v>2.380805525961052</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.824887779508069</v>
+        <v>1.610670237078058</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.690952893418824</v>
+        <v>0.658527617824044</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.229469301682938</v>
+        <v>1.135505609740307</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.863511725208485</v>
+        <v>1.169594884896454</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.689066327363759</v>
+        <v>1.038439992023852</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.588954006875858</v>
+        <v>0.9081639712930193</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.064864973848261</v>
+        <v>1.031438671780444</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.49782958658432</v>
+        <v>2.984403630540094</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.170406228904857</v>
+        <v>1.406147223356393</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.003395875234777</v>
+        <v>0.8922494774406432</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.213581592527573</v>
+        <v>3.326973788271761</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.175306610899963</v>
+        <v>0.8375696922347226</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.856052707297369</v>
+        <v>1.236729106592458</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.2189200488784</v>
+        <v>1.29675927661025</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.71531212907377</v>
+        <v>1.271292927413016</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.811081109999685</v>
+        <v>3.985339824427837</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.06271720063544</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.093329097609153</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.843392529276222</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.565102022661127</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>2.113351811810364</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.570238342290105</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.086872635397336</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.682299197441924</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>3.858483443964237</v>
+        <v>1.296235927918088</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.034151531117812</v>
+        <v>2.877960413600056</v>
       </c>
       <c r="C30" t="n">
-        <v>1.896841526277696</v>
+        <v>2.34632084918824</v>
       </c>
       <c r="D30" t="n">
-        <v>2.562656112398503</v>
+        <v>2.702520474759384</v>
       </c>
       <c r="E30" t="n">
-        <v>2.018301643032597</v>
+        <v>3.95050666996126</v>
       </c>
       <c r="F30" t="n">
-        <v>3.806042092010863</v>
+        <v>4.13739535484964</v>
       </c>
       <c r="G30" t="n">
-        <v>3.769248946566149</v>
+        <v>3.76161582746525</v>
       </c>
       <c r="H30" t="n">
-        <v>3.746567716354166</v>
+        <v>7.015792779171941</v>
       </c>
       <c r="I30" t="n">
-        <v>6.027295985214432</v>
+        <v>4.136495181224197</v>
       </c>
       <c r="J30" t="n">
-        <v>3.966295005968251</v>
+        <v>1.579569404448488</v>
       </c>
       <c r="K30" t="n">
-        <v>2.720191884953463</v>
+        <v>2.041990882567362</v>
       </c>
       <c r="L30" t="n">
-        <v>3.069200581254869</v>
+        <v>2.831879165416709</v>
       </c>
       <c r="M30" t="n">
-        <v>6.100201392499649</v>
+        <v>2.014407112523771</v>
       </c>
       <c r="N30" t="n">
-        <v>3.174632537173314</v>
+        <v>1.888898035943174</v>
       </c>
       <c r="O30" t="n">
-        <v>2.399541302860467</v>
+        <v>2.937370362681257</v>
       </c>
       <c r="P30" t="n">
-        <v>3.562139313472837</v>
+        <v>1.254868508149009</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.358564425438321</v>
+        <v>2.940808920954778</v>
       </c>
       <c r="R30" t="n">
-        <v>4.025523607428865</v>
+        <v>3.567090430787848</v>
       </c>
       <c r="S30" t="n">
-        <v>1.695227897245297</v>
+        <v>1.989972000246785</v>
       </c>
       <c r="T30" t="n">
-        <v>3.941388758687628</v>
+        <v>2.802134102145604</v>
       </c>
       <c r="U30" t="n">
-        <v>1.461036090872295</v>
+        <v>0.3906871579912007</v>
       </c>
       <c r="V30" t="n">
-        <v>2.543550425036059</v>
+        <v>2.596747127162128</v>
       </c>
       <c r="W30" t="n">
-        <v>1.490464037511712</v>
+        <v>2.755759676279142</v>
       </c>
       <c r="X30" t="n">
-        <v>1.149201617368112</v>
+        <v>1.933977389301806</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.820254114661104</v>
+        <v>1.74580666084289</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.439390781019609</v>
+        <v>0.6202408047879713</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.7794920348125159</v>
+        <v>1.100771406951136</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.423388822000337</v>
+        <v>0.8716465186174606</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.863511725208485</v>
+        <v>1.169594884896454</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.636480873914728</v>
+        <v>0.8008387720428642</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.222139619444544</v>
+        <v>1.118024621055826</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.02338151366723</v>
+        <v>0.9898336470737237</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.941069353653932</v>
+        <v>3.331672513579756</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.369008408434006</v>
+        <v>1.836283504873087</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.9457438976074983</v>
+        <v>1.222063735442433</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.8217972244340955</v>
+        <v>3.804595535396332</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.358940177375829</v>
+        <v>0.882414483193366</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.661375799271542</v>
+        <v>0.4638481061682915</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.7459076747435553</v>
+        <v>0.7336221871106147</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.448167289193542</v>
+        <v>0.7050680034105794</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.695826196072458</v>
+        <v>4.109285847171342</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.757163156534945</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0.8555712154917412</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.207768742264979</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.291838448250288</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.5117272943684</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.882612854597555</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.179458843372721</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.009136365364023</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.477958610360913</v>
+        <v>0.743519804257624</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.83542823355383</v>
+        <v>2.463272442148764</v>
       </c>
       <c r="C31" t="n">
-        <v>2.077273393925416</v>
+        <v>1.996660438991536</v>
       </c>
       <c r="D31" t="n">
-        <v>2.140544253309525</v>
+        <v>2.223894961991335</v>
       </c>
       <c r="E31" t="n">
-        <v>2.44332264317636</v>
+        <v>3.433470227604394</v>
       </c>
       <c r="F31" t="n">
-        <v>3.796646126798873</v>
+        <v>3.479420369584623</v>
       </c>
       <c r="G31" t="n">
-        <v>3.56749145439984</v>
+        <v>3.101875284964149</v>
       </c>
       <c r="H31" t="n">
-        <v>3.499200093241177</v>
+        <v>6.730779893603294</v>
       </c>
       <c r="I31" t="n">
-        <v>5.881970424850311</v>
+        <v>4.236838305804484</v>
       </c>
       <c r="J31" t="n">
-        <v>3.237325453903068</v>
+        <v>2.071984037014824</v>
       </c>
       <c r="K31" t="n">
-        <v>2.616313965722692</v>
+        <v>1.600898726362088</v>
       </c>
       <c r="L31" t="n">
-        <v>3.565845591870778</v>
+        <v>2.257625015795768</v>
       </c>
       <c r="M31" t="n">
-        <v>4.794445224069894</v>
+        <v>1.616617486267168</v>
       </c>
       <c r="N31" t="n">
-        <v>2.113449487623336</v>
+        <v>2.35693546253743</v>
       </c>
       <c r="O31" t="n">
-        <v>1.74197342923425</v>
+        <v>2.484558682822073</v>
       </c>
       <c r="P31" t="n">
-        <v>4.065876223213546</v>
+        <v>1.664021977794225</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.824610178454943</v>
+        <v>3.088354697371261</v>
       </c>
       <c r="R31" t="n">
-        <v>4.402418372502093</v>
+        <v>3.408285552856515</v>
       </c>
       <c r="S31" t="n">
-        <v>1.928731800700181</v>
+        <v>1.80339860746935</v>
       </c>
       <c r="T31" t="n">
-        <v>3.575440025513434</v>
+        <v>2.22237569092704</v>
       </c>
       <c r="U31" t="n">
-        <v>2.552745294161307</v>
+        <v>1.031309073271962</v>
       </c>
       <c r="V31" t="n">
-        <v>2.67337182178162</v>
+        <v>2.048449193873574</v>
       </c>
       <c r="W31" t="n">
-        <v>1.995525310214713</v>
+        <v>2.140103936027708</v>
       </c>
       <c r="X31" t="n">
-        <v>1.078696262733853</v>
+        <v>1.660169721173468</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.827711372698106</v>
+        <v>1.895406641246565</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.028881108125789</v>
+        <v>1.065575150952187</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.071205961412449</v>
+        <v>1.105256468305269</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.042403317953217</v>
+        <v>0.8475752109817781</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.689066327363759</v>
+        <v>1.038439992023852</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.636480873914728</v>
+        <v>0.8008387720428642</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.212014377245271</v>
+        <v>0.7122250445602617</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.613560330180227</v>
+        <v>1.206567718460368</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.649851757116138</v>
+        <v>3.818158339872424</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.9833239309565541</v>
+        <v>1.343388662326572</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.080617630723485</v>
+        <v>1.188994526896036</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.618681533230396</v>
+        <v>4.120503972835992</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.537195027338058</v>
+        <v>0.3667169230839324</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.7138920802585957</v>
+        <v>0.5815700330169339</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.63286301459119</v>
+        <v>1.112390515734712</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.727799304362247</v>
+        <v>0.7357297538939885</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.170490760715721</v>
+        <v>3.711304713227297</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.997247226813188</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.503210182414922</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.714305790446868</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.855653420650411</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.957128684395768</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1.383467314406809</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.507770251962628</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.148693536643104</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>4.499886243287897</v>
+        <v>0.3859428668197297</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.137483973817779</v>
+        <v>2.582244207954044</v>
       </c>
       <c r="C32" t="n">
-        <v>2.473735044514949</v>
+        <v>1.796871063436556</v>
       </c>
       <c r="D32" t="n">
-        <v>2.550519824724071</v>
+        <v>2.045880490963417</v>
       </c>
       <c r="E32" t="n">
-        <v>2.451088450655909</v>
+        <v>3.203036052255961</v>
       </c>
       <c r="F32" t="n">
-        <v>4.008577423067319</v>
+        <v>3.090007058603561</v>
       </c>
       <c r="G32" t="n">
-        <v>3.443874949700824</v>
+        <v>2.868256711916591</v>
       </c>
       <c r="H32" t="n">
-        <v>3.613664650267925</v>
+        <v>6.215668597559294</v>
       </c>
       <c r="I32" t="n">
-        <v>6.305724813432653</v>
+        <v>3.760527475866588</v>
       </c>
       <c r="J32" t="n">
-        <v>3.497344681091107</v>
+        <v>2.11318997126452</v>
       </c>
       <c r="K32" t="n">
-        <v>2.044590980803523</v>
+        <v>1.219411161224731</v>
       </c>
       <c r="L32" t="n">
-        <v>3.163831519452224</v>
+        <v>1.985131336672907</v>
       </c>
       <c r="M32" t="n">
-        <v>5.936788537430702</v>
+        <v>1.259820818341581</v>
       </c>
       <c r="N32" t="n">
-        <v>3.17129160141228</v>
+        <v>2.017850603417626</v>
       </c>
       <c r="O32" t="n">
-        <v>2.264162064925697</v>
+        <v>2.05702834449341</v>
       </c>
       <c r="P32" t="n">
-        <v>4.097791976501092</v>
+        <v>1.844794021013509</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.814121251857993</v>
+        <v>3.047853194792874</v>
       </c>
       <c r="R32" t="n">
-        <v>3.91463956926683</v>
+        <v>3.58769774518928</v>
       </c>
       <c r="S32" t="n">
-        <v>1.954794562040666</v>
+        <v>2.07443524777963</v>
       </c>
       <c r="T32" t="n">
-        <v>3.889329174287273</v>
+        <v>2.12974565314225</v>
       </c>
       <c r="U32" t="n">
-        <v>1.972767629166409</v>
+        <v>1.320084206933019</v>
       </c>
       <c r="V32" t="n">
-        <v>2.217359389673586</v>
+        <v>2.202719001257997</v>
       </c>
       <c r="W32" t="n">
-        <v>2.065317779235284</v>
+        <v>2.086432571116173</v>
       </c>
       <c r="X32" t="n">
-        <v>1.638522227040172</v>
+        <v>1.830923945617742</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.31796442107603</v>
+        <v>2.028445415739116</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.658786534611409</v>
+        <v>1.268597919004157</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.6203366648858754</v>
+        <v>1.241517042633105</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.056513308317701</v>
+        <v>1.237931698513108</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.588954006875858</v>
+        <v>0.9081639712930193</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.222139619444544</v>
+        <v>1.118024621055826</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.212014377245271</v>
+        <v>0.7122250445602617</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.347267036607306</v>
+        <v>0.8796012668323033</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.168089016924028</v>
+        <v>3.58658083682694</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.431312659722906</v>
+        <v>1.379216417902948</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.153782833929387</v>
+        <v>0.6697954172611091</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.153189906189643</v>
+        <v>4.056718961972074</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.549442032420716</v>
+        <v>0.7079704163333649</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.63631021329222</v>
+        <v>0.9861994025729094</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.173871768209856</v>
+        <v>1.490460750409053</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.583175944379812</v>
+        <v>1.311352775826261</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.201215055574079</v>
+        <v>3.845913203158376</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.89927512930763</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.181189287278249</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.362551964540783</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.582003946381115</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.001471088088771</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.699458568923472</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.367606022384978</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0.9198394290130497</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>4.405834414134608</v>
+        <v>1.041186833603703</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.109687850100078</v>
+        <v>2.927571835371731</v>
       </c>
       <c r="C33" t="n">
-        <v>3.162972798298362</v>
+        <v>2.312801911985534</v>
       </c>
       <c r="D33" t="n">
-        <v>3.383251952766924</v>
+        <v>2.604477850897752</v>
       </c>
       <c r="E33" t="n">
-        <v>2.746252263254926</v>
+        <v>3.721107695070564</v>
       </c>
       <c r="F33" t="n">
-        <v>4.230239998010522</v>
+        <v>3.753101881182012</v>
       </c>
       <c r="G33" t="n">
-        <v>3.6813334931568</v>
+        <v>3.482805701109222</v>
       </c>
       <c r="H33" t="n">
-        <v>3.922560609444316</v>
+        <v>6.155494606809734</v>
       </c>
       <c r="I33" t="n">
-        <v>6.190591118035172</v>
+        <v>3.315324648404669</v>
       </c>
       <c r="J33" t="n">
-        <v>3.853871344926323</v>
+        <v>1.92568825500655</v>
       </c>
       <c r="K33" t="n">
-        <v>2.493709688516188</v>
+        <v>1.889050953008158</v>
       </c>
       <c r="L33" t="n">
-        <v>3.255415053506383</v>
+        <v>2.647681899551818</v>
       </c>
       <c r="M33" t="n">
-        <v>5.672282882642319</v>
+        <v>1.814925619685314</v>
       </c>
       <c r="N33" t="n">
-        <v>3.510047437280175</v>
+        <v>1.51595842997723</v>
       </c>
       <c r="O33" t="n">
-        <v>2.959310141703846</v>
+        <v>2.502132118092772</v>
       </c>
       <c r="P33" t="n">
-        <v>4.658406425696818</v>
+        <v>1.778351826222712</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.537244902037281</v>
+        <v>2.784276625587514</v>
       </c>
       <c r="R33" t="n">
-        <v>3.922730774371407</v>
+        <v>3.665888003967494</v>
       </c>
       <c r="S33" t="n">
-        <v>2.403136351395824</v>
+        <v>2.229149271491141</v>
       </c>
       <c r="T33" t="n">
-        <v>3.483362721516619</v>
+        <v>2.611870328829557</v>
       </c>
       <c r="U33" t="n">
-        <v>2.069215916393971</v>
+        <v>1.138000411953126</v>
       </c>
       <c r="V33" t="n">
-        <v>2.536773397835975</v>
+        <v>2.608659445446385</v>
       </c>
       <c r="W33" t="n">
-        <v>2.80020099704855</v>
+        <v>2.566664975903326</v>
       </c>
       <c r="X33" t="n">
-        <v>2.190745776101511</v>
+        <v>2.054513269354043</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.137669757690254</v>
+        <v>2.120556849807095</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.890103319918011</v>
+        <v>1.022494043953063</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.694362720716827</v>
+        <v>1.41911542166559</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.089109494262575</v>
+        <v>1.40380071673294</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.064864973848261</v>
+        <v>1.031438671780444</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.02338151366723</v>
+        <v>0.9898336470737237</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.613560330180227</v>
+        <v>1.206567718460368</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.347267036607306</v>
+        <v>0.8796012668323033</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.605763681163198</v>
+        <v>2.965820593256081</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.288447994717141</v>
+        <v>1.853360807135849</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.107546257790017</v>
+        <v>0.6176398251491667</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.247594623253706</v>
+        <v>3.805203913714449</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.550412431534125</v>
+        <v>1.176086838306572</v>
       </c>
       <c r="AM33" t="n">
-        <v>2.276736772069355</v>
+        <v>1.149990827194912</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.207336677374649</v>
+        <v>1.542154904540637</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.699826100011128</v>
+        <v>1.550251389469147</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.228413341705589</v>
+        <v>4.092725332950879</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2.953512549815268</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.234123238484817</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>3.213744759435305</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.748379443176307</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.095279310053311</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.600853579347357</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.099444872817375</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>2.052335499485898</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>4.417993479612018</v>
+        <v>1.36768141867227</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.52103924422064</v>
+        <v>5.868099003853419</v>
       </c>
       <c r="C34" t="n">
-        <v>1.81387117860102</v>
+        <v>3.611878334303272</v>
       </c>
       <c r="D34" t="n">
-        <v>2.127550928704923</v>
+        <v>4.071936384493574</v>
       </c>
       <c r="E34" t="n">
-        <v>1.839284801822375</v>
+        <v>6.419842103342641</v>
       </c>
       <c r="F34" t="n">
-        <v>3.50165888160974</v>
+        <v>6.116871047886439</v>
       </c>
       <c r="G34" t="n">
-        <v>4.770187499708779</v>
+        <v>5.102243909230399</v>
       </c>
       <c r="H34" t="n">
-        <v>3.157943928051839</v>
+        <v>6.8154383556217</v>
       </c>
       <c r="I34" t="n">
-        <v>6.11120370596357</v>
+        <v>2.856634134179819</v>
       </c>
       <c r="J34" t="n">
-        <v>3.572829269335234</v>
+        <v>2.941396359700861</v>
       </c>
       <c r="K34" t="n">
-        <v>4.123705458333339</v>
+        <v>3.828698477628884</v>
       </c>
       <c r="L34" t="n">
-        <v>4.534949347828912</v>
+        <v>4.832317244374789</v>
       </c>
       <c r="M34" t="n">
-        <v>5.78631153900666</v>
+        <v>3.590521055710323</v>
       </c>
       <c r="N34" t="n">
-        <v>3.430643700031561</v>
+        <v>2.159958581877348</v>
       </c>
       <c r="O34" t="n">
-        <v>2.76547992646932</v>
+        <v>3.791601909831546</v>
       </c>
       <c r="P34" t="n">
-        <v>4.496012967409215</v>
+        <v>3.324560657640434</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.463552346461784</v>
+        <v>2.162834565408593</v>
       </c>
       <c r="R34" t="n">
-        <v>6.73687900375859</v>
+        <v>3.91129883944127</v>
       </c>
       <c r="S34" t="n">
-        <v>1.970544831926039</v>
+        <v>3.482294240734142</v>
       </c>
       <c r="T34" t="n">
-        <v>3.205425129064021</v>
+        <v>4.254125897818796</v>
       </c>
       <c r="U34" t="n">
-        <v>3.591228634763765</v>
+        <v>3.091969985724856</v>
       </c>
       <c r="V34" t="n">
-        <v>4.201127517626403</v>
+        <v>4.551372912195271</v>
       </c>
       <c r="W34" t="n">
-        <v>3.754724670414315</v>
+        <v>4.604112478272261</v>
       </c>
       <c r="X34" t="n">
-        <v>2.314537726987675</v>
+        <v>3.549818405532627</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.145718052748702</v>
+        <v>4.34616128245009</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.896906746255839</v>
+        <v>3.615070001277931</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.812823171041951</v>
+        <v>3.070144219468097</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.04441080433856</v>
+        <v>3.636528494668117</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.49782958658432</v>
+        <v>2.984403630540094</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.941069353653932</v>
+        <v>3.331672513579756</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.649851757116138</v>
+        <v>3.818158339872424</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.168089016924028</v>
+        <v>3.58658083682694</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.605763681163198</v>
+        <v>2.965820593256081</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.266360195719104</v>
+        <v>4.142650700486051</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.450630837241833</v>
+        <v>3.030558745189379</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.677058912738455</v>
+        <v>2.539552481805565</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.922211208914806</v>
+        <v>3.623747959409735</v>
       </c>
       <c r="AM34" t="n">
-        <v>2.39204212181819</v>
+        <v>3.616557716975811</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.638810352431635</v>
+        <v>3.347336448641387</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.41531089849166</v>
+        <v>3.725949994529933</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.982874517318749</v>
+        <v>6.314404446855351</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.122448954990632</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.400542298097364</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.386576777428997</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.979497994945222</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.160528022360332</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.278023275677765</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.622369771574431</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>2.494367185534446</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>4.751329099195636</v>
+        <v>3.919963545450879</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.167876996721846</v>
+        <v>2.76755078311863</v>
       </c>
       <c r="C35" t="n">
-        <v>1.717077660355675</v>
+        <v>1.887586590784991</v>
       </c>
       <c r="D35" t="n">
-        <v>1.961415797183034</v>
+        <v>1.545111043378842</v>
       </c>
       <c r="E35" t="n">
-        <v>2.307655257729125</v>
+        <v>3.847147639702772</v>
       </c>
       <c r="F35" t="n">
-        <v>3.999851457605303</v>
+        <v>3.40884759825219</v>
       </c>
       <c r="G35" t="n">
-        <v>4.067895963866187</v>
+        <v>2.837210830600512</v>
       </c>
       <c r="H35" t="n">
-        <v>3.718705822737599</v>
+        <v>6.008678339481532</v>
       </c>
       <c r="I35" t="n">
-        <v>6.295374475646561</v>
+        <v>4.511907194140209</v>
       </c>
       <c r="J35" t="n">
-        <v>3.619218079754964</v>
+        <v>2.454642793750884</v>
       </c>
       <c r="K35" t="n">
-        <v>3.052537643688217</v>
+        <v>1.609804707957751</v>
       </c>
       <c r="L35" t="n">
-        <v>3.917564462519106</v>
+        <v>1.388782601341425</v>
       </c>
       <c r="M35" t="n">
-        <v>5.256685976832711</v>
+        <v>1.391083684576235</v>
       </c>
       <c r="N35" t="n">
-        <v>2.188358789437952</v>
+        <v>2.84575137576105</v>
       </c>
       <c r="O35" t="n">
-        <v>1.923098178894712</v>
+        <v>2.243086575922804</v>
       </c>
       <c r="P35" t="n">
-        <v>4.070892406072132</v>
+        <v>1.995556006617987</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.779173366544244</v>
+        <v>3.340237159847848</v>
       </c>
       <c r="R35" t="n">
-        <v>4.81198395253496</v>
+        <v>3.399706066324322</v>
       </c>
       <c r="S35" t="n">
-        <v>1.903059469401551</v>
+        <v>2.272972852951041</v>
       </c>
       <c r="T35" t="n">
-        <v>4.015157493427473</v>
+        <v>1.927707759975827</v>
       </c>
       <c r="U35" t="n">
-        <v>2.662209386753143</v>
+        <v>1.887891010445718</v>
       </c>
       <c r="V35" t="n">
-        <v>3.120166706903084</v>
+        <v>1.343837780869456</v>
       </c>
       <c r="W35" t="n">
-        <v>1.786962755323623</v>
+        <v>1.337640773906595</v>
       </c>
       <c r="X35" t="n">
-        <v>0.9188486117249713</v>
+        <v>2.294151908225823</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.046874787929621</v>
+        <v>2.047208266268132</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.578980998226942</v>
+        <v>2.088374640685719</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.9384836696475081</v>
+        <v>1.551798881974777</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.163296086353139</v>
+        <v>1.150645414238359</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.170406228904857</v>
+        <v>1.406147223356393</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.369008408434006</v>
+        <v>1.836283504873087</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.9833239309565541</v>
+        <v>1.343388662326572</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.431312659722906</v>
+        <v>1.379216417902948</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.288447994717141</v>
+        <v>1.853360807135849</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.266360195719104</v>
+        <v>4.142650700486051</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.4462313590159647</v>
+        <v>1.88764306128788</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.028236394286471</v>
+        <v>3.889351217000997</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.8808809239986171</v>
+        <v>1.482527009327506</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.716798400852551</v>
+        <v>1.865862202796228</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.068740807605918</v>
+        <v>1.893091230653088</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.327807961726142</v>
+        <v>1.607631777366167</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.279529780470358</v>
+        <v>2.766942076109415</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53910861354113</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0.9162085319000358</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.004526864291552</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1.503917469216738</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.413391144037306</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.306464543355239</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.573695425114425</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0.8032725844626295</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>4.492712613880859</v>
+        <v>1.636035152775755</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.793152551379146</v>
+        <v>3.06486120916249</v>
       </c>
       <c r="C36" t="n">
-        <v>1.731583596137645</v>
+        <v>1.900078827848789</v>
       </c>
       <c r="D36" t="n">
-        <v>2.100829954835224</v>
+        <v>2.302649269438164</v>
       </c>
       <c r="E36" t="n">
-        <v>2.163367349694101</v>
+        <v>3.506022759227386</v>
       </c>
       <c r="F36" t="n">
-        <v>3.945072188150091</v>
+        <v>3.386741503848449</v>
       </c>
       <c r="G36" t="n">
-        <v>3.94501117174642</v>
+        <v>3.049409705696527</v>
       </c>
       <c r="H36" t="n">
-        <v>3.698884563095074</v>
+        <v>6.142695862557433</v>
       </c>
       <c r="I36" t="n">
-        <v>6.26493834688218</v>
+        <v>3.201568873494679</v>
       </c>
       <c r="J36" t="n">
-        <v>3.692581750199519</v>
+        <v>2.058101426917263</v>
       </c>
       <c r="K36" t="n">
-        <v>2.857114784016639</v>
+        <v>1.457892824551916</v>
       </c>
       <c r="L36" t="n">
-        <v>3.641561980152447</v>
+        <v>2.458640476455428</v>
       </c>
       <c r="M36" t="n">
-        <v>5.574022271722481</v>
+        <v>1.453232121985528</v>
       </c>
       <c r="N36" t="n">
-        <v>2.524177029654865</v>
+        <v>1.569013170743587</v>
       </c>
       <c r="O36" t="n">
-        <v>2.029062931972775</v>
+        <v>2.040923941394796</v>
       </c>
       <c r="P36" t="n">
-        <v>3.924880854956946</v>
+        <v>1.967539680142923</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.62513371542644</v>
+        <v>2.686478236163066</v>
       </c>
       <c r="R36" t="n">
-        <v>4.535716983273317</v>
+        <v>3.536934684978274</v>
       </c>
       <c r="S36" t="n">
-        <v>1.762166565735673</v>
+        <v>2.084599441822351</v>
       </c>
       <c r="T36" t="n">
-        <v>3.992067020703459</v>
+        <v>2.319609917060998</v>
       </c>
       <c r="U36" t="n">
-        <v>2.279202173088249</v>
+        <v>1.34526473591448</v>
       </c>
       <c r="V36" t="n">
-        <v>2.885016932022149</v>
+        <v>2.587783401559939</v>
       </c>
       <c r="W36" t="n">
-        <v>1.617466565675103</v>
+        <v>2.465771099907084</v>
       </c>
       <c r="X36" t="n">
-        <v>0.8817091708855901</v>
+        <v>1.810277455078494</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.275644796750353</v>
+        <v>2.38290396617161</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.367179885740202</v>
+        <v>1.381080777713996</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.5726766816071727</v>
+        <v>1.314378832387651</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.068669086905067</v>
+        <v>1.598745624224217</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.003395875234777</v>
+        <v>0.8922494774406432</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.9457438976074983</v>
+        <v>1.222063735442433</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.080617630723485</v>
+        <v>1.188994526896036</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.153782833929387</v>
+        <v>0.6697954172611091</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.107546257790017</v>
+        <v>0.6176398251491667</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.450630837241833</v>
+        <v>3.030558745189379</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.4462313590159647</v>
+        <v>1.88764306128788</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.645083370597455</v>
+        <v>3.840732720566437</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.8182203593447628</v>
+        <v>1.036071745205632</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.973151634277678</v>
+        <v>1.191807727104287</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.6727637942867054</v>
+        <v>1.626460271763113</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.196442996024658</v>
+        <v>1.6280765514412</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.261038740244787</v>
+        <v>4.341670374939423</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.465660111986707</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0.5697294813888533</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>1.375101584612654</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1.284120300395264</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1.315239039270455</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.38442629829854</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.345145479137781</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0.5449194977783239</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>4.221661607205381</v>
+        <v>1.421250243369962</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.66814477546247</v>
+        <v>6.370145365242873</v>
       </c>
       <c r="C37" t="n">
-        <v>1.992875543972147</v>
+        <v>3.28176613896112</v>
       </c>
       <c r="D37" t="n">
-        <v>2.389260439908373</v>
+        <v>3.502768103620437</v>
       </c>
       <c r="E37" t="n">
-        <v>2.166210801047081</v>
+        <v>7.177529601085388</v>
       </c>
       <c r="F37" t="n">
-        <v>4.114607444644896</v>
+        <v>6.546669545961946</v>
       </c>
       <c r="G37" t="n">
-        <v>4.079734345002512</v>
+        <v>5.240750469309348</v>
       </c>
       <c r="H37" t="n">
-        <v>3.828985762303552</v>
+        <v>7.40963077222301</v>
       </c>
       <c r="I37" t="n">
-        <v>6.565896351557909</v>
+        <v>4.831301709233617</v>
       </c>
       <c r="J37" t="n">
-        <v>3.94019715189531</v>
+        <v>2.769714277409263</v>
       </c>
       <c r="K37" t="n">
-        <v>2.84042316004201</v>
+        <v>3.810849212232521</v>
       </c>
       <c r="L37" t="n">
-        <v>3.602401343169296</v>
+        <v>4.450355848965041</v>
       </c>
       <c r="M37" t="n">
-        <v>6.213695436131242</v>
+        <v>3.477265489329593</v>
       </c>
       <c r="N37" t="n">
-        <v>3.137789735622434</v>
+        <v>3.071349467835561</v>
       </c>
       <c r="O37" t="n">
-        <v>2.429388262706389</v>
+        <v>3.977273501799498</v>
       </c>
       <c r="P37" t="n">
-        <v>4.022197561836952</v>
+        <v>3.071042251314517</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.725772797452833</v>
+        <v>2.934726800205464</v>
       </c>
       <c r="R37" t="n">
-        <v>4.53339483865706</v>
+        <v>3.85644526774809</v>
       </c>
       <c r="S37" t="n">
-        <v>1.847681602682102</v>
+        <v>3.79151542620836</v>
       </c>
       <c r="T37" t="n">
-        <v>4.20453561432382</v>
+        <v>4.360053046252661</v>
       </c>
       <c r="U37" t="n">
-        <v>2.100785993415658</v>
+        <v>3.445195361182615</v>
       </c>
       <c r="V37" t="n">
-        <v>2.906201989631552</v>
+        <v>4.360218905562918</v>
       </c>
       <c r="W37" t="n">
-        <v>1.837166229006027</v>
+        <v>4.521979265228896</v>
       </c>
       <c r="X37" t="n">
-        <v>1.386619436505264</v>
+        <v>4.091036465966348</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.439178399731049</v>
+        <v>4.177973689488202</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.236718990720947</v>
+        <v>4.296629434147268</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.6837423822935208</v>
+        <v>3.078637719374058</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.383397300425969</v>
+        <v>3.575312943549963</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.213581592527573</v>
+        <v>3.326973788271761</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.8217972244340955</v>
+        <v>3.804595535396332</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.618681533230396</v>
+        <v>4.120503972835992</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.153189906189643</v>
+        <v>4.056718961972074</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.247594623253706</v>
+        <v>3.805203913714449</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.677058912738455</v>
+        <v>2.539552481805565</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.028236394286471</v>
+        <v>3.889351217000997</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.645083370597455</v>
+        <v>3.840732720566437</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.9036870240596656</v>
+        <v>4.015493952094932</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.600601474222822</v>
+        <v>4.111257347933118</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.1390287267891927</v>
+        <v>3.394569480728046</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.2293071198772</v>
+        <v>3.779717716295072</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.214054073528721</v>
+        <v>5.929580096216942</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.455600185626852</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0.3226199071948406</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.837344195744659</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1.275696097242945</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1.479799644682118</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.705222174097826</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.467130675570335</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0.6935195642198281</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>4.196143962419211</v>
+        <v>4.286001461226414</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.127888445093437</v>
+        <v>2.70911501329111</v>
       </c>
       <c r="C38" t="n">
-        <v>1.364080612380015</v>
+        <v>1.831465820596917</v>
       </c>
       <c r="D38" t="n">
-        <v>1.605313598468903</v>
+        <v>2.134625752533136</v>
       </c>
       <c r="E38" t="n">
-        <v>1.768035688314414</v>
+        <v>3.513322839444588</v>
       </c>
       <c r="F38" t="n">
-        <v>3.562460461381697</v>
+        <v>3.476518702638048</v>
       </c>
       <c r="G38" t="n">
-        <v>3.857955165458317</v>
+        <v>2.915062048010552</v>
       </c>
       <c r="H38" t="n">
-        <v>3.199416453260925</v>
+        <v>6.67708817367729</v>
       </c>
       <c r="I38" t="n">
-        <v>6.165861162284587</v>
+        <v>3.994545548943039</v>
       </c>
       <c r="J38" t="n">
-        <v>3.327908829157866</v>
+        <v>2.123918275193016</v>
       </c>
       <c r="K38" t="n">
-        <v>2.819753231293329</v>
+        <v>1.524473387842974</v>
       </c>
       <c r="L38" t="n">
-        <v>3.592255347602804</v>
+        <v>2.358108193966262</v>
       </c>
       <c r="M38" t="n">
-        <v>5.931032945631254</v>
+        <v>1.521256280645763</v>
       </c>
       <c r="N38" t="n">
-        <v>2.929937141320415</v>
+        <v>2.29006114173616</v>
       </c>
       <c r="O38" t="n">
-        <v>1.899102313065016</v>
+        <v>2.269259148966144</v>
       </c>
       <c r="P38" t="n">
-        <v>3.765657757995385</v>
+        <v>1.791325262639618</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.455112299694319</v>
+        <v>2.794524287438581</v>
       </c>
       <c r="R38" t="n">
-        <v>5.099806812551913</v>
+        <v>3.151722375618288</v>
       </c>
       <c r="S38" t="n">
-        <v>1.391433648792235</v>
+        <v>1.524058883282909</v>
       </c>
       <c r="T38" t="n">
-        <v>3.741188086128129</v>
+        <v>2.024459766586453</v>
       </c>
       <c r="U38" t="n">
-        <v>2.451386540067586</v>
+        <v>1.048920842860947</v>
       </c>
       <c r="V38" t="n">
-        <v>2.926291745759881</v>
+        <v>2.030556778183251</v>
       </c>
       <c r="W38" t="n">
-        <v>2.232055033042219</v>
+        <v>2.112780266108095</v>
       </c>
       <c r="X38" t="n">
-        <v>1.238363747274376</v>
+        <v>1.333421114471073</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.819688980830223</v>
+        <v>2.199400714418817</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.138296376896564</v>
+        <v>1.227422419927771</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.118631882430354</v>
+        <v>0.9692908597764655</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.404940865653469</v>
+        <v>1.039784115027303</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.175306610899963</v>
+        <v>0.8375696922347226</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.358940177375829</v>
+        <v>0.882414483193366</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.537195027338058</v>
+        <v>0.3667169230839324</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.549442032420716</v>
+        <v>0.7079704163333649</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.550412431534125</v>
+        <v>1.176086838306572</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.922211208914806</v>
+        <v>3.623747959409735</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.8808809239986171</v>
+        <v>1.482527009327506</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.8182203593447628</v>
+        <v>1.036071745205632</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.9036870240596656</v>
+        <v>4.015493952094932</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.318314447069482</v>
+        <v>0.6439853024357228</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.9203696340754999</v>
+        <v>1.157213159867595</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.7768921416586477</v>
+        <v>0.8708821842907946</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.7926422538634041</v>
+        <v>3.928266715348234</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.7862372990059698</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.6198995881131789</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.513681188343944</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.240194121170149</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.55370000414641</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.094644220198037</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.286501645309832</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0.6919496511346959</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>4.284769596135184</v>
+        <v>0.566685224000876</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.159676222668797</v>
+        <v>2.681395002374118</v>
       </c>
       <c r="C39" t="n">
-        <v>1.628375060984118</v>
+        <v>2.265862738961046</v>
       </c>
       <c r="D39" t="n">
-        <v>1.755456461919874</v>
+        <v>2.654490132259402</v>
       </c>
       <c r="E39" t="n">
-        <v>2.426876807829015</v>
+        <v>3.611222067483443</v>
       </c>
       <c r="F39" t="n">
-        <v>3.678952462412513</v>
+        <v>3.838423755427461</v>
       </c>
       <c r="G39" t="n">
-        <v>3.691155836522928</v>
+        <v>3.531068598370324</v>
       </c>
       <c r="H39" t="n">
-        <v>3.480309505107764</v>
+        <v>7.086082651461268</v>
       </c>
       <c r="I39" t="n">
-        <v>5.763421018149517</v>
+        <v>4.211045446513419</v>
       </c>
       <c r="J39" t="n">
-        <v>3.255378571536125</v>
+        <v>1.872676467275508</v>
       </c>
       <c r="K39" t="n">
-        <v>2.923317345202551</v>
+        <v>1.902574344197026</v>
       </c>
       <c r="L39" t="n">
-        <v>3.731056601669293</v>
+        <v>2.748525036671109</v>
       </c>
       <c r="M39" t="n">
-        <v>4.692887743974262</v>
+        <v>1.957167825206619</v>
       </c>
       <c r="N39" t="n">
-        <v>1.748602521614415</v>
+        <v>2.126276552599873</v>
       </c>
       <c r="O39" t="n">
-        <v>1.450164436554436</v>
+        <v>2.826998306972636</v>
       </c>
       <c r="P39" t="n">
-        <v>3.778766747190505</v>
+        <v>1.551012934133084</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.550174986022399</v>
+        <v>3.075579354777991</v>
       </c>
       <c r="R39" t="n">
-        <v>4.66373111216954</v>
+        <v>3.587473988483855</v>
       </c>
       <c r="S39" t="n">
-        <v>1.919487522089702</v>
+        <v>1.9267396034744</v>
       </c>
       <c r="T39" t="n">
-        <v>3.761730663304094</v>
+        <v>2.66559895881958</v>
       </c>
       <c r="U39" t="n">
-        <v>2.778921879230911</v>
+        <v>0.7608548744314158</v>
       </c>
       <c r="V39" t="n">
-        <v>2.90966180652548</v>
+        <v>2.563287015052407</v>
       </c>
       <c r="W39" t="n">
-        <v>1.766545425676303</v>
+        <v>2.686744680475955</v>
       </c>
       <c r="X39" t="n">
-        <v>0.7924024715186906</v>
+        <v>1.776456766970755</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.26238336512733</v>
+        <v>1.90560712104736</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.80170471406718</v>
+        <v>0.744327567336437</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.259535587634105</v>
+        <v>1.192252123050213</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.051510405487078</v>
+        <v>1.061225236291691</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.856052707297369</v>
+        <v>1.236729106592458</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.661375799271542</v>
+        <v>0.4638481061682915</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.7138920802585957</v>
+        <v>0.5815700330169339</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.63631021329222</v>
+        <v>0.9861994025729094</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.276736772069355</v>
+        <v>1.149990827194912</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.39204212181819</v>
+        <v>3.616557716975811</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.716798400852551</v>
+        <v>1.865862202796228</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.973151634277678</v>
+        <v>1.191807727104287</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.600601474222822</v>
+        <v>4.111257347933118</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.318314447069482</v>
+        <v>0.6439853024357228</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.628112096292704</v>
+        <v>0.9108545378559925</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.490461930665941</v>
+        <v>0.7152772372752293</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.783443791610711</v>
+        <v>4.175218000170768</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.743024430532972</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.447793081061386</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.146156914005909</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.614595378854028</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1.514676563453752</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>1.141401393963912</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.511742617854738</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.140600153405801</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>4.416713102944806</v>
+        <v>0.468421910597786</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.613232271592097</v>
+        <v>3.37400989759034</v>
       </c>
       <c r="C40" t="n">
-        <v>1.960215476270131</v>
+        <v>2.091640513870106</v>
       </c>
       <c r="D40" t="n">
-        <v>2.421701285640561</v>
+        <v>2.513421480875125</v>
       </c>
       <c r="E40" t="n">
-        <v>2.067496935318757</v>
+        <v>4.395513974808634</v>
       </c>
       <c r="F40" t="n">
-        <v>4.069209447627083</v>
+        <v>4.433234715499704</v>
       </c>
       <c r="G40" t="n">
-        <v>4.085038853311533</v>
+        <v>3.856997373728408</v>
       </c>
       <c r="H40" t="n">
-        <v>3.805560657553781</v>
+        <v>7.390698364220722</v>
       </c>
       <c r="I40" t="n">
-        <v>6.518814343796151</v>
+        <v>4.522859221725735</v>
       </c>
       <c r="J40" t="n">
-        <v>3.960209139375868</v>
+        <v>1.196261399387875</v>
       </c>
       <c r="K40" t="n">
-        <v>2.860209570326336</v>
+        <v>1.988928187666916</v>
       </c>
       <c r="L40" t="n">
-        <v>3.552223986129818</v>
+        <v>2.842210017537986</v>
       </c>
       <c r="M40" t="n">
-        <v>6.229621094489018</v>
+        <v>1.939426568825785</v>
       </c>
       <c r="N40" t="n">
-        <v>3.178896565444341</v>
+        <v>1.98326821043841</v>
       </c>
       <c r="O40" t="n">
-        <v>2.46497217248785</v>
+        <v>2.987009438228443</v>
       </c>
       <c r="P40" t="n">
-        <v>4.001754728045382</v>
+        <v>0.8459195868872418</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.716432893098393</v>
+        <v>2.908138184188437</v>
       </c>
       <c r="R40" t="n">
-        <v>4.543667335878508</v>
+        <v>3.44393431773595</v>
       </c>
       <c r="S40" t="n">
-        <v>1.77735390263312</v>
+        <v>1.975336564400672</v>
       </c>
       <c r="T40" t="n">
-        <v>4.126700726937258</v>
+        <v>2.896342852694319</v>
       </c>
       <c r="U40" t="n">
-        <v>1.998583159107221</v>
+        <v>0.501286644709706</v>
       </c>
       <c r="V40" t="n">
-        <v>2.90101552721031</v>
+        <v>2.686134287960026</v>
       </c>
       <c r="W40" t="n">
-        <v>1.861924924396287</v>
+        <v>2.910405390271638</v>
       </c>
       <c r="X40" t="n">
-        <v>1.352080550989854</v>
+        <v>2.043767400403246</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.449322249500447</v>
+        <v>1.740725903627074</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.298840786954081</v>
+        <v>1.297227315717864</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.6986866399877142</v>
+        <v>0.8315221075835265</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.448707732716423</v>
+        <v>0.8491831394321234</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2189200488784</v>
+        <v>1.29675927661025</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.7459076747435553</v>
+        <v>0.7336221871106147</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.63286301459119</v>
+        <v>1.112390515734712</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.173871768209856</v>
+        <v>1.490460750409053</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.207336677374649</v>
+        <v>1.542154904540637</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.638810352431635</v>
+        <v>3.347336448641387</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.068740807605918</v>
+        <v>1.893091230653088</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.6727637942867054</v>
+        <v>1.626460271763113</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.1390287267891927</v>
+        <v>3.394569480728046</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.9203696340754999</v>
+        <v>1.157213159867595</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.628112096292704</v>
+        <v>0.9108545378559925</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.268809602973148</v>
+        <v>0.5307082766266988</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.232437167831733</v>
+        <v>4.310948574993279</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.480739384055148</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.3132787411367336</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>1.900440722738027</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>1.327602551313355</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.546972590454649</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>1.746901803159474</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.436662362090973</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0.738823193446975</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>4.091638877516112</v>
+        <v>1.103351079907992</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.879844216681536</v>
+        <v>2.941942855637415</v>
       </c>
       <c r="C41" t="n">
-        <v>1.337384359955523</v>
+        <v>2.118072054430893</v>
       </c>
       <c r="D41" t="n">
-        <v>1.303612949000471</v>
+        <v>2.417203877455667</v>
       </c>
       <c r="E41" t="n">
-        <v>1.967404933060535</v>
+        <v>4.064395053860341</v>
       </c>
       <c r="F41" t="n">
-        <v>3.189237725435067</v>
+        <v>4.13647237391841</v>
       </c>
       <c r="G41" t="n">
-        <v>3.244162441628913</v>
+        <v>3.604671452484394</v>
       </c>
       <c r="H41" t="n">
-        <v>2.855351439937112</v>
+        <v>7.268397212953369</v>
       </c>
       <c r="I41" t="n">
-        <v>5.76764202136274</v>
+        <v>4.621500958539882</v>
       </c>
       <c r="J41" t="n">
-        <v>2.925998426642234</v>
+        <v>1.660564787349676</v>
       </c>
       <c r="K41" t="n">
-        <v>2.317825261105366</v>
+        <v>1.930018257827868</v>
       </c>
       <c r="L41" t="n">
-        <v>3.111143723723339</v>
+        <v>2.626600139730461</v>
       </c>
       <c r="M41" t="n">
-        <v>6.069198655213944</v>
+        <v>1.90015002473467</v>
       </c>
       <c r="N41" t="n">
-        <v>3.104831284800083</v>
+        <v>2.346713849899271</v>
       </c>
       <c r="O41" t="n">
-        <v>1.481101189934132</v>
+        <v>2.909599783234684</v>
       </c>
       <c r="P41" t="n">
-        <v>3.173238181782653</v>
+        <v>1.194326696529445</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.835723252002751</v>
+        <v>3.066696348754805</v>
       </c>
       <c r="R41" t="n">
-        <v>4.742537203138858</v>
+        <v>3.382737999607018</v>
       </c>
       <c r="S41" t="n">
-        <v>1.404330028705971</v>
+        <v>1.840793077080721</v>
       </c>
       <c r="T41" t="n">
-        <v>3.764359279063907</v>
+        <v>2.64096820772565</v>
       </c>
       <c r="U41" t="n">
-        <v>2.387013398405951</v>
+        <v>0.7117059902199535</v>
       </c>
       <c r="V41" t="n">
-        <v>2.383415651154893</v>
+        <v>2.334113493634191</v>
       </c>
       <c r="W41" t="n">
-        <v>2.138000870648754</v>
+        <v>2.576529728278102</v>
       </c>
       <c r="X41" t="n">
-        <v>1.442404178076632</v>
+        <v>1.877379457799754</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.183629865425844</v>
+        <v>1.724786020911638</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.550073945758242</v>
+        <v>1.189962245511973</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.274214875767389</v>
+        <v>0.9463818807555641</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.15233521719633</v>
+        <v>0.6281803712175099</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.71531212907377</v>
+        <v>1.271292927413016</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.448167289193542</v>
+        <v>0.7050680034105794</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.727799304362247</v>
+        <v>0.7357297538939885</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.583175944379812</v>
+        <v>1.311352775826261</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.699826100011128</v>
+        <v>1.550251389469147</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.41531089849166</v>
+        <v>3.725949994529933</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.327807961726142</v>
+        <v>1.607631777366167</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.196442996024658</v>
+        <v>1.6280765514412</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.2293071198772</v>
+        <v>3.779717716295072</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.7768921416586477</v>
+        <v>0.8708821842907946</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.490461930665941</v>
+        <v>0.7152772372752293</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.268809602973148</v>
+        <v>0.5307082766266988</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.246482638088276</v>
+        <v>3.938082724962476</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.4688727209290143</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.011555796533353</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.854148569891843</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.6579502816296566</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.327370201956213</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0.7988366634734888</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0.9644938368307837</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.8081698285934373</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>4.145062211093206</v>
+        <v>0.6811241162120194</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.624136316022163</v>
+        <v>3.210304018689361</v>
       </c>
       <c r="C42" t="n">
-        <v>1.496831622826213</v>
+        <v>4.552272913851311</v>
       </c>
       <c r="D42" t="n">
-        <v>1.944209178126846</v>
+        <v>3.904776080458087</v>
       </c>
       <c r="E42" t="n">
-        <v>2.108952347642785</v>
+        <v>4.903396226404682</v>
       </c>
       <c r="F42" t="n">
-        <v>3.946622198482324</v>
+        <v>4.650042387887825</v>
       </c>
       <c r="G42" t="n">
-        <v>4.455439992351216</v>
+        <v>4.499658676005396</v>
       </c>
       <c r="H42" t="n">
-        <v>3.69099292307357</v>
+        <v>5.928886031383377</v>
       </c>
       <c r="I42" t="n">
-        <v>6.522917189828399</v>
+        <v>6.282663321707092</v>
       </c>
       <c r="J42" t="n">
-        <v>3.909138112714628</v>
+        <v>4.829013923097542</v>
       </c>
       <c r="K42" t="n">
-        <v>3.498157234504568</v>
+        <v>4.256243819150352</v>
       </c>
       <c r="L42" t="n">
-        <v>4.106864530829387</v>
+        <v>3.241474707197515</v>
       </c>
       <c r="M42" t="n">
-        <v>6.222620564969068</v>
+        <v>4.066593577227199</v>
       </c>
       <c r="N42" t="n">
-        <v>3.108771544587116</v>
+        <v>5.2498844488108</v>
       </c>
       <c r="O42" t="n">
-        <v>2.390136753845732</v>
+        <v>4.523007796616731</v>
       </c>
       <c r="P42" t="n">
-        <v>3.931559812004689</v>
+        <v>4.287265726399268</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.709759584025474</v>
+        <v>5.46042507619392</v>
       </c>
       <c r="R42" t="n">
-        <v>5.510025446546909</v>
+        <v>5.050293010135589</v>
       </c>
       <c r="S42" t="n">
-        <v>1.921488570739536</v>
+        <v>4.411017515933349</v>
       </c>
       <c r="T42" t="n">
-        <v>4.286366781775484</v>
+        <v>3.792542595319389</v>
       </c>
       <c r="U42" t="n">
-        <v>2.869227887668818</v>
+        <v>4.233586579737097</v>
       </c>
       <c r="V42" t="n">
-        <v>3.551477565627547</v>
+        <v>2.666426507809103</v>
       </c>
       <c r="W42" t="n">
-        <v>2.354606360765603</v>
+        <v>2.729128295699009</v>
       </c>
       <c r="X42" t="n">
-        <v>1.628277106346315</v>
+        <v>4.503741960682847</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.271290737880581</v>
+        <v>3.774884013842722</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.401317374410673</v>
+        <v>4.07085075763876</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.687198053894617</v>
+        <v>4.192795891314408</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.979499971665102</v>
+        <v>3.474289573655004</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.811081109999685</v>
+        <v>3.985339824427837</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.695826196072458</v>
+        <v>4.109285847171342</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.170490760715721</v>
+        <v>3.711304713227297</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.201215055574079</v>
+        <v>3.845913203158376</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.228413341705589</v>
+        <v>4.092725332950879</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.982874517318749</v>
+        <v>6.314404446855351</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.279529780470358</v>
+        <v>2.766942076109415</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.261038740244787</v>
+        <v>4.341670374939423</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.214054073528721</v>
+        <v>5.929580096216942</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.7926422538634041</v>
+        <v>3.928266715348234</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.783443791610711</v>
+        <v>4.175218000170768</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.232437167831733</v>
+        <v>4.310948574993279</v>
       </c>
       <c r="AO42" t="n">
-        <v>1.246482638088276</v>
+        <v>3.938082724962476</v>
       </c>
       <c r="AP42" t="n">
         <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.160635623997682</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.068209317104435</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.480015173842989</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>1.550134161798952</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1.56525624603259</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>1.689037840421559</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.891842580442603</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.346599209254962</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>4.384799218693563</v>
+        <v>3.818701551105045</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.200478622861888</v>
+        <v>2.424374895912297</v>
       </c>
       <c r="C43" t="n">
-        <v>1.284621996836779</v>
+        <v>2.304753944810723</v>
       </c>
       <c r="D43" t="n">
-        <v>1.178242272148823</v>
+        <v>2.559297712195765</v>
       </c>
       <c r="E43" t="n">
-        <v>1.813564628997005</v>
+        <v>3.518911049681491</v>
       </c>
       <c r="F43" t="n">
-        <v>3.09401503282264</v>
+        <v>3.72036675313466</v>
       </c>
       <c r="G43" t="n">
-        <v>3.412448776809675</v>
+        <v>3.354164965358734</v>
       </c>
       <c r="H43" t="n">
-        <v>2.677928578686425</v>
+        <v>7.013575698670995</v>
       </c>
       <c r="I43" t="n">
-        <v>5.829342419473956</v>
+        <v>4.392194330490327</v>
       </c>
       <c r="J43" t="n">
-        <v>2.862461575591942</v>
+        <v>2.169104641498236</v>
       </c>
       <c r="K43" t="n">
-        <v>2.527546603460831</v>
+        <v>1.954642061405643</v>
       </c>
       <c r="L43" t="n">
-        <v>3.271276835817683</v>
+        <v>2.608185113972275</v>
       </c>
       <c r="M43" t="n">
-        <v>6.24869415485869</v>
+        <v>1.982315515276136</v>
       </c>
       <c r="N43" t="n">
-        <v>3.329634530563882</v>
+        <v>2.514726048841695</v>
       </c>
       <c r="O43" t="n">
-        <v>1.652661530386227</v>
+        <v>2.812233016006298</v>
       </c>
       <c r="P43" t="n">
-        <v>3.290156757359957</v>
+        <v>1.745986676732899</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.002849794740383</v>
+        <v>3.169791953336476</v>
       </c>
       <c r="R43" t="n">
-        <v>5.184483652090709</v>
+        <v>3.454594480009683</v>
       </c>
       <c r="S43" t="n">
-        <v>1.336052700006867</v>
+        <v>1.807842688350391</v>
       </c>
       <c r="T43" t="n">
-        <v>3.660457914479184</v>
+        <v>2.450437221308105</v>
       </c>
       <c r="U43" t="n">
-        <v>2.589997084314835</v>
+        <v>1.013628562022854</v>
       </c>
       <c r="V43" t="n">
-        <v>2.644438671140047</v>
+        <v>2.217234269971782</v>
       </c>
       <c r="W43" t="n">
-        <v>2.551568904218874</v>
+        <v>2.386111633477983</v>
       </c>
       <c r="X43" t="n">
-        <v>1.688622068262221</v>
+        <v>1.684423865721694</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.931699337477177</v>
+        <v>1.973142966349604</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.883189371833949</v>
+        <v>0.9520055043436831</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.605061475773355</v>
+        <v>1.291879624048919</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.571969341343863</v>
+        <v>0.9669988387291477</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.06271720063544</v>
+        <v>1.296235927918088</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.757163156534945</v>
+        <v>0.743519804257624</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.997247226813188</v>
+        <v>0.3859428668197297</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.89927512930763</v>
+        <v>1.041186833603703</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.953512549815268</v>
+        <v>1.36768141867227</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.122448954990632</v>
+        <v>3.919963545450879</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.53910861354113</v>
+        <v>1.636035152775755</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.465660111986707</v>
+        <v>1.421250243369962</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.455600185626852</v>
+        <v>4.286001461226414</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.7862372990059698</v>
+        <v>0.566685224000876</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.743024430532972</v>
+        <v>0.468421910597786</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.480739384055148</v>
+        <v>1.103351079907992</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.4688727209290143</v>
+        <v>0.6811241162120194</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.160635623997682</v>
+        <v>3.818701551105045</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.20108777097061</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>1.978928951529353</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>1.086496045931246</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1.687437046580103</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0.9396320811412752</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>1.229790174289204</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.115549453398442</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>4.26147445126755</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2.701429895385591</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1.717726649208481</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2.119488790312546</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1.900793037335625</v>
-      </c>
-      <c r="F44" t="n">
-        <v>3.837594288693076</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.921105747443788</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3.543409903279155</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6.337934794929509</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.688188974187648</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.747236968117948</v>
-      </c>
-      <c r="L44" t="n">
-        <v>3.474169972194221</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.100967351257824</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.065947649089136</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.20973146361895</v>
-      </c>
-      <c r="P44" t="n">
-        <v>3.860120429726317</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.553178532138805</v>
-      </c>
-      <c r="R44" t="n">
-        <v>4.666914486592042</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1.558679069686868</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.933873998650396</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.066030010115374</v>
-      </c>
-      <c r="V44" t="n">
-        <v>2.806850904951221</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.930040518075831</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.215747719369396</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>3.271513490288398</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.146009621531414</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.6923819011705493</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.318984653068658</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.093329097609153</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.8555712154917412</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.503210182414922</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.181189287278249</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>2.234123238484817</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>2.400542298097364</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0.9162085319000358</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.5697294813888533</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0.3226199071948406</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0.6198995881131789</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.447793081061386</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0.3132787411367336</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>1.011555796533353</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.068209317104435</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.20108777097061</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>1.75397165726581</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>1.190376163007801</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.484632114375471</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>1.462988281193758</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.254857658163558</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.5264757691883514</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>4.104203984196667</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4.045614037238421</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1.965485142217091</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2.043256549483683</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2.981611117946978</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4.398873166510248</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4.598363514542604</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4.158935764112488</v>
-      </c>
-      <c r="I45" t="n">
-        <v>6.561127963912391</v>
-      </c>
-      <c r="J45" t="n">
-        <v>3.930564860698718</v>
-      </c>
-      <c r="K45" t="n">
-        <v>3.779732763405617</v>
-      </c>
-      <c r="L45" t="n">
-        <v>4.661973002637553</v>
-      </c>
-      <c r="M45" t="n">
-        <v>4.94066498884226</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.739835409601472</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.123802672383694</v>
-      </c>
-      <c r="P45" t="n">
-        <v>4.330048376102801</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.132438770400412</v>
-      </c>
-      <c r="R45" t="n">
-        <v>5.395491410928596</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.615216712377542</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4.621481158480967</v>
-      </c>
-      <c r="U45" t="n">
-        <v>3.562500257895514</v>
-      </c>
-      <c r="V45" t="n">
-        <v>3.848818325238063</v>
-      </c>
-      <c r="W45" t="n">
-        <v>2.086991161730877</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.553172504197522</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.498659090140482</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.051825480488616</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.888009067097615</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.789799587511845</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.843392529276222</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.207768742264979</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.714305790446868</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2.362551964540783</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>3.213744759435305</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>2.386576777428997</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.004526864291552</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.375101584612654</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.837344195744659</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1.513681188343944</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.146156914005909</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.900440722738027</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>1.854148569891843</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.480015173842989</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1.978928951529353</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.75397165726581</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>1.995218865028087</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>1.541244680400969</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>1.718772830480537</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>2.338288625277966</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1.67255976142556</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>5.042043978166392</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>2.596928242262631</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1.632500214505278</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1.740857884739241</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.370599132386231</v>
-      </c>
-      <c r="F46" t="n">
-        <v>3.420767904426287</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.186842402402223</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3.245460047845185</v>
-      </c>
-      <c r="I46" t="n">
-        <v>5.763560198457551</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.256042266902419</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.305223563230656</v>
-      </c>
-      <c r="L46" t="n">
-        <v>3.005743945846298</v>
-      </c>
-      <c r="M46" t="n">
-        <v>6.117829487833998</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.100668506207317</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.629600296830036</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.967574562539701</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.6554130928955</v>
-      </c>
-      <c r="R46" t="n">
-        <v>4.218418245858501</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.807786718308561</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4.146784204430781</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.292599625273194</v>
-      </c>
-      <c r="V46" t="n">
-        <v>2.240744994208669</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.670858128461325</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.50669832872713</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>3.540357240079344</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0.3882320636365378</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.26616952624539</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.02119418666207</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.565102022661127</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.291838448250288</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.855653420650411</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.582003946381115</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.748379443176307</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>2.979497994945222</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.503917469216738</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.284120300395264</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.275696097242945</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1.240194121170149</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1.614595378854028</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1.327602551313355</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0.6579502816296566</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.550134161798952</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.086496045931246</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.190376163007801</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>1.995218865028087</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0.9188110336850001</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>1.206015308602053</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>1.06826310249406</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0.9886780289882338</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>3.986737449126057</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3.070553379585092</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1.829591874728016</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.107479195044353</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2.881993089883172</v>
-      </c>
-      <c r="F47" t="n">
-        <v>4.003266562731248</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3.843887757371701</v>
-      </c>
-      <c r="H47" t="n">
-        <v>3.958036585080387</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6.072674734232137</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3.868899520637922</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.085597657593254</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3.710688900162207</v>
-      </c>
-      <c r="M47" t="n">
-        <v>5.739145229780394</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.576035594089041</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.933334282507433</v>
-      </c>
-      <c r="P47" t="n">
-        <v>3.293671085975035</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.116254572979454</v>
-      </c>
-      <c r="R47" t="n">
-        <v>4.293296398739748</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.403340427862094</v>
-      </c>
-      <c r="T47" t="n">
-        <v>4.705960024269339</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.792453605378375</v>
-      </c>
-      <c r="V47" t="n">
-        <v>2.962435918110109</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.120412609380144</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.480000920221219</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>3.303456172434698</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.131791027809913</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.534166072295377</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.289190274753421</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.113351811810364</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.5117272943684</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.957128684395768</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.001471088088771</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>3.095279310053311</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>3.160528022360332</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.413391144037306</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.315239039270455</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.479799644682118</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>1.55370000414641</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1.514676563453752</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1.546972590454649</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>1.327370201956213</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.56525624603259</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.687437046580103</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>1.484632114375471</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>1.541244680400969</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0.9188110336850001</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>1.650947210878116</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>1.726916452238452</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.382087597885556</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>4.198825530287512</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3.152563112281334</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1.393834676403988</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.8688440682296441</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.146862541489461</v>
-      </c>
-      <c r="F48" t="n">
-        <v>3.024870167969944</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3.028167701801558</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2.600808120316618</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5.49929650629475</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.39766628262616</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.264966049709135</v>
-      </c>
-      <c r="L48" t="n">
-        <v>3.243603066918455</v>
-      </c>
-      <c r="M48" t="n">
-        <v>5.434739148909964</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.661645395642367</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.8718411042912625</v>
-      </c>
-      <c r="P48" t="n">
-        <v>3.301243229397302</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.006903166698121</v>
-      </c>
-      <c r="R48" t="n">
-        <v>4.879217914717471</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1.497844181046533</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.474373492432314</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.758027223947439</v>
-      </c>
-      <c r="V48" t="n">
-        <v>2.390530442611282</v>
-      </c>
-      <c r="W48" t="n">
-        <v>2.347214936333498</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.415390324570892</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>3.244986349059971</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.248569224014129</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.490719641084378</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.057710455255011</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.570238342290105</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.882612854597555</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.383467314406809</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.699458568923472</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.600853579347357</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>2.278023275677765</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.306464543355239</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.38442629829854</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.705222174097826</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.094644220198037</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.141401393963912</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.746901803159474</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0.7988366634734888</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.689037840421559</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.9396320811412752</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.462988281193758</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>1.718772830480537</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>1.206015308602053</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>1.650947210878116</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.134250858732355</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.063795381019056</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>4.463215842572732</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>2.136722083022957</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1.39287407752899</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.719732166667033</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1.615740794276131</v>
-      </c>
-      <c r="F49" t="n">
-        <v>2.762279698054969</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.771190079386263</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2.619029385624564</v>
-      </c>
-      <c r="I49" t="n">
-        <v>5.170567046187133</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.83027611098738</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1.957252498995127</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.371844698353303</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5.872013357577286</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.176537389324415</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1.508983205136552</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.879242668282736</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.599574616886748</v>
-      </c>
-      <c r="R49" t="n">
-        <v>4.250500399237159</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.9614911180200391</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.139423755345609</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.656701691051205</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.77576214051689</v>
-      </c>
-      <c r="W49" t="n">
-        <v>2.060127529909015</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.194655329616539</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>3.790710460936306</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.231093030810275</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.178060765344452</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.182472966576926</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.086872635397336</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.179458843372721</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.507770251962628</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.367606022384978</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.099444872817375</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>2.622369771574431</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.573695425114425</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.345145479137781</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.467130675570335</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.286501645309832</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.511742617854738</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.436662362090973</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0.9644938368307837</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.891842580442603</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.229790174289204</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.254857658163558</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.338288625277966</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1.06826310249406</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.726916452238452</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.134250858732355</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.01346953882034</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>3.49543826302846</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>2.614315912258247</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1.69333690752963</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1.841397424373548</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2.034949927272149</v>
-      </c>
-      <c r="F50" t="n">
-        <v>3.651511387529203</v>
-      </c>
-      <c r="G50" t="n">
-        <v>3.528925360713774</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3.307994920587777</v>
-      </c>
-      <c r="I50" t="n">
-        <v>6.095394709630816</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.290396672170222</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.374369529490967</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3.293724588143917</v>
-      </c>
-      <c r="M50" t="n">
-        <v>5.805271511884539</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.824109287017292</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.785268075104492</v>
-      </c>
-      <c r="P50" t="n">
-        <v>3.70142683645913</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.363081595721432</v>
-      </c>
-      <c r="R50" t="n">
-        <v>4.456058947663544</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.523067504987589</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.803110661137406</v>
-      </c>
-      <c r="U50" t="n">
-        <v>2.153595069654111</v>
-      </c>
-      <c r="V50" t="n">
-        <v>2.473053537077742</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.847560674375352</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.114816913338288</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>3.442009176065232</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.019177259490367</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.5150434747615754</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.8356208253508683</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.682299197441924</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.009136365364023</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.148693536643104</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0.9198394290130497</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>2.052335499485898</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>2.494367185534446</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0.8032725844626295</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.5449194977783239</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0.6935195642198281</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0.6919496511346959</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.140600153405801</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>0.738823193446975</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0.8081698285934373</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.346599209254962</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.115549453398442</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0.5264757691883514</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>1.67255976142556</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.9886780289882338</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.382087597885556</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>1.063795381019056</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.01346953882034</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>4.22896813231085</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3.182601296843855</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3.541830449024862</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4.636378590123875</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3.290392574695071</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3.64055856367011</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4.575437532632748</v>
-      </c>
-      <c r="H51" t="n">
-        <v>4.543100053573835</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4.551252427162149</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.449509403476958</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4.671619492059961</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3.038170735835759</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7.467247810626188</v>
-      </c>
-      <c r="N51" t="n">
-        <v>5.467600645643432</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.461268247312252</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3.089477167424934</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3.199596059997461</v>
-      </c>
-      <c r="R51" t="n">
-        <v>5.054458878015742</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.441130313806064</v>
-      </c>
-      <c r="T51" t="n">
-        <v>4.154304383797016</v>
-      </c>
-      <c r="U51" t="n">
-        <v>2.682300912645847</v>
-      </c>
-      <c r="V51" t="n">
-        <v>3.928845773350701</v>
-      </c>
-      <c r="W51" t="n">
-        <v>3.924437807003848</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.680715148047694</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>5.591926167399</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>4.176663893563307</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>4.147203818301882</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>4.413564924658966</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.858483443964237</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.477958610360913</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>4.499886243287897</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>4.405834414134608</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>4.417993479612018</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>4.751329099195636</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>4.492712613880859</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>4.221661607205381</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>4.196143962419211</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>4.284769596135184</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>4.416713102944806</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>4.091638877516112</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>4.145062211093206</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>4.384799218693563</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>4.26147445126755</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>4.104203984196667</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>5.042043978166392</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.986737449126057</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>4.198825530287512</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>4.463215842572732</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>3.49543826302846</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>4.22896813231085</v>
-      </c>
-      <c r="AY51" t="n">
         <v>0</v>
       </c>
     </row>
